--- a/andean_associations/Andean Associations.xlsx
+++ b/andean_associations/Andean Associations.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wgu/Desktop/CMSNetwork/andean_associations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{312C7197-0CDB-0742-BAC2-03303524619C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0E1BE9D-BB1D-F941-88D4-8F93093C6AD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25680" yWindow="660" windowWidth="25360" windowHeight="20780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/andean_associations/Andean Associations.xlsx
+++ b/andean_associations/Andean Associations.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wgu/Desktop/CMSNetwork/andean_associations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0E1BE9D-BB1D-F941-88D4-8F93093C6AD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38473A16-FB1C-874B-9015-7CB3FB7ADE57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25680" yWindow="660" windowWidth="25360" windowHeight="20780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -794,10 +794,10 @@
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C2">
         <v>40</v>
@@ -812,178 +812,178 @@
         <v>20</v>
       </c>
       <c r="G2">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="H2">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J2">
-        <v>-4.7185569472057598E-2</v>
+        <v>-1.6259321142582519E-2</v>
       </c>
       <c r="K2">
-        <v>5.7818179204794538E-3</v>
+        <v>8.568065626575629E-4</v>
       </c>
       <c r="L2">
-        <v>4.1114686624065602E-2</v>
+        <v>-6.6664480117853446E-3</v>
       </c>
       <c r="M2">
-        <v>3.4918829747855713E-2</v>
+        <v>0.26562208591984687</v>
       </c>
       <c r="N2">
-        <v>-1.5547630000597491E-3</v>
+        <v>-4.9512265248954869E-4</v>
       </c>
       <c r="O2">
-        <v>4.317374094577825E-2</v>
+        <v>4.4754234391201783E-2</v>
       </c>
       <c r="P2" t="s">
         <v>22</v>
       </c>
       <c r="Q2">
-        <v>6.3599997125273991E-2</v>
+        <v>9.4248721892331924E-3</v>
       </c>
       <c r="R2">
         <v>6</v>
       </c>
       <c r="S2">
-        <v>133073425</v>
+        <v>13284922</v>
       </c>
       <c r="T2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="C3">
         <v>40</v>
       </c>
       <c r="D3">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F3">
         <v>20</v>
       </c>
       <c r="G3">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="H3">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J3">
-        <v>-7.8321264046306016E-2</v>
+        <v>-1.095546499963147</v>
       </c>
       <c r="K3">
-        <v>8.6503849923604253E-3</v>
+        <v>9.1975840020432531E-4</v>
       </c>
       <c r="L3">
-        <v>1.1581395121537949E-2</v>
+        <v>-0.41315654599708468</v>
       </c>
       <c r="M3">
-        <v>0.72348059088520011</v>
+        <v>0.30851175888574051</v>
       </c>
       <c r="N3">
-        <v>-3.409057496971778E-3</v>
+        <v>-2.733741813760043E-2</v>
       </c>
       <c r="O3">
-        <v>1.389916755741271E-2</v>
+        <v>9.8981671127009827E-2</v>
       </c>
       <c r="P3" t="s">
         <v>22</v>
       </c>
       <c r="Q3">
-        <v>9.5154234915964683E-2</v>
+        <v>1.011734240224758E-2</v>
       </c>
       <c r="R3">
         <v>6</v>
       </c>
       <c r="S3">
-        <v>133073425</v>
+        <v>13284922</v>
       </c>
       <c r="T3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="C4">
         <v>40</v>
       </c>
       <c r="D4">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F4">
         <v>20</v>
       </c>
       <c r="G4">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="H4">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J4">
-        <v>-0.2036002241316634</v>
+        <v>-0.14205413296616129</v>
       </c>
       <c r="K4">
-        <v>1.023784786689722E-2</v>
+        <v>2.081624073858525E-3</v>
       </c>
       <c r="L4">
-        <v>0.169482382798293</v>
+        <v>9.4352205965898842E-2</v>
       </c>
       <c r="M4">
-        <v>5.8723928208935447E-2</v>
+        <v>0.1040460824239669</v>
       </c>
       <c r="N4">
-        <v>-2.8484723019942941E-3</v>
+        <v>-4.1054188763062988E-3</v>
       </c>
       <c r="O4">
-        <v>0.42046138787926468</v>
+        <v>8.0312127033090708E-2</v>
       </c>
       <c r="P4" t="s">
         <v>22</v>
       </c>
       <c r="Q4">
-        <v>0.11261632653586939</v>
+        <v>2.2897864812443769E-2</v>
       </c>
       <c r="R4">
         <v>6</v>
       </c>
       <c r="S4">
-        <v>133073425</v>
+        <v>13284922</v>
       </c>
       <c r="T4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="C5">
         <v>40</v>
@@ -998,46 +998,46 @@
         <v>20</v>
       </c>
       <c r="G5">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="H5">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>-0.1331189176788026</v>
+        <v>-2.073018440140515E-3</v>
       </c>
       <c r="K5">
-        <v>1.1016011494016729E-2</v>
+        <v>3.1492180990437459E-3</v>
       </c>
       <c r="L5">
-        <v>0.1506252201867532</v>
+        <v>1.304024876802637E-3</v>
       </c>
       <c r="M5">
-        <v>1.35913743220105E-2</v>
+        <v>0.1407043601238136</v>
       </c>
       <c r="N5">
-        <v>-4.052326142109844E-3</v>
+        <v>-7.1615803903430991E-5</v>
       </c>
       <c r="O5">
-        <v>8.5410763737419237E-2</v>
+        <v>4.7726814047783311E-2</v>
       </c>
       <c r="P5" t="s">
         <v>22</v>
       </c>
       <c r="Q5">
-        <v>0.1211761264341841</v>
+        <v>3.4641399089481197E-2</v>
       </c>
       <c r="R5">
         <v>6</v>
       </c>
       <c r="S5">
-        <v>133073425</v>
+        <v>13284922</v>
       </c>
       <c r="T5" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.2">
@@ -1045,7 +1045,7 @@
         <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="C6">
         <v>40</v>
@@ -1069,28 +1069,28 @@
         <v>2</v>
       </c>
       <c r="J6">
-        <v>-1.982562158167456</v>
+        <v>-4.7185569472057598E-2</v>
       </c>
       <c r="K6">
-        <v>1.170929601608142E-2</v>
+        <v>5.7818179204794538E-3</v>
       </c>
       <c r="L6">
-        <v>-1.200690089334536</v>
+        <v>4.1114686624065602E-2</v>
       </c>
       <c r="M6">
-        <v>0.1760500357135035</v>
+        <v>3.4918829747855713E-2</v>
       </c>
       <c r="N6">
-        <v>-6.2295022081060088E-2</v>
+        <v>-1.5547630000597491E-3</v>
       </c>
       <c r="O6">
-        <v>7.8871703667559523E-2</v>
+        <v>4.317374094577825E-2</v>
       </c>
       <c r="P6" t="s">
         <v>22</v>
       </c>
       <c r="Q6">
-        <v>0.12880225617689561</v>
+        <v>6.3599997125273991E-2</v>
       </c>
       <c r="R6">
         <v>6</v>
@@ -1104,10 +1104,10 @@
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="C7">
         <v>40</v>
@@ -1122,54 +1122,54 @@
         <v>20</v>
       </c>
       <c r="G7">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H7">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I7">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J7">
-        <v>-4.750300229395929E-2</v>
+        <v>2.2661035835246768</v>
       </c>
       <c r="K7">
-        <v>1.182244492197717E-2</v>
+        <v>5.9187859599574601E-3</v>
       </c>
       <c r="L7">
-        <v>-5.9297576250654837E-5</v>
+        <v>-2.0964034252115709</v>
       </c>
       <c r="M7">
-        <v>0.99772319308620461</v>
+        <v>9.0457591391094133E-2</v>
       </c>
       <c r="N7">
-        <v>-1.612938888258437E-3</v>
+        <v>-3.2371214242875708E-2</v>
       </c>
       <c r="O7">
-        <v>6.1507301934860092E-2</v>
+        <v>0.49214785518683102</v>
       </c>
       <c r="P7" t="s">
         <v>22</v>
       </c>
       <c r="Q7">
-        <v>0.13004689414174889</v>
+        <v>6.5106645559532064E-2</v>
       </c>
       <c r="R7">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="S7">
-        <v>133073425</v>
+        <v>2128865</v>
       </c>
       <c r="T7" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="C8">
         <v>40</v>
@@ -1184,232 +1184,220 @@
         <v>20</v>
       </c>
       <c r="G8">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="H8">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="I8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>-4.6352608530592893E-2</v>
+        <v>0.19616165625288989</v>
       </c>
       <c r="K8">
-        <v>1.2633176341423E-2</v>
+        <v>6.8073684116259619E-3</v>
       </c>
       <c r="L8">
-        <v>3.2440671343286917E-2</v>
+        <v>5.8552663515730997E-2</v>
       </c>
       <c r="M8">
-        <v>0.12384303283971571</v>
+        <v>0.20972011051297329</v>
       </c>
       <c r="N8">
-        <v>-1.3848172371075751E-3</v>
+        <v>-3.3662396458685379E-3</v>
       </c>
       <c r="O8">
-        <v>9.7775863025042806E-2</v>
+        <v>7.7512667228128274E-2</v>
       </c>
       <c r="P8" t="s">
         <v>22</v>
       </c>
       <c r="Q8">
-        <v>0.13896493975565299</v>
+        <v>7.4881052527885586E-2</v>
       </c>
       <c r="R8">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S8">
-        <v>133073425</v>
+        <v>121821143</v>
       </c>
       <c r="T8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>36</v>
       </c>
       <c r="C9">
         <v>40</v>
       </c>
       <c r="D9">
+        <v>37</v>
+      </c>
+      <c r="E9">
+        <v>17</v>
+      </c>
+      <c r="F9">
+        <v>20</v>
+      </c>
+      <c r="G9">
+        <v>25</v>
+      </c>
+      <c r="H9">
         <v>12</v>
-      </c>
-      <c r="E9">
-        <v>6</v>
-      </c>
-      <c r="F9">
-        <v>6</v>
-      </c>
-      <c r="G9">
-        <v>6</v>
-      </c>
-      <c r="H9">
-        <v>6</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9">
-        <v>-12.517542184017829</v>
+        <v>0.16446577887063091</v>
       </c>
       <c r="K9">
-        <v>3.0191759373752711E-2</v>
+        <v>6.8882139630185926E-3</v>
       </c>
       <c r="L9">
-        <v>-0.48984399872651319</v>
+        <v>0.11159834567703091</v>
       </c>
       <c r="M9">
-        <v>0.90878713933809718</v>
+        <v>4.9357051286708427E-2</v>
       </c>
       <c r="N9">
-        <v>-0.48110792741165259</v>
+        <v>-2.5423995537246251E-3</v>
       </c>
       <c r="O9">
-        <v>2.92983987629159E-2</v>
+        <v>0.23970748349274321</v>
       </c>
       <c r="P9" t="s">
         <v>22</v>
       </c>
       <c r="Q9">
-        <v>0.30191759373752708</v>
+        <v>7.5770353593204526E-2</v>
       </c>
       <c r="R9">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="S9">
-        <v>133073425</v>
+        <v>42607288</v>
       </c>
       <c r="T9" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="C10">
         <v>40</v>
       </c>
       <c r="D10">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E10">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F10">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H10">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J10">
-        <v>19.86724225142359</v>
+        <v>-22.803341363151539</v>
       </c>
       <c r="K10">
-        <v>3.3448702010404931E-2</v>
-      </c>
-      <c r="L10">
-        <v>0.24187050553734829</v>
-      </c>
-      <c r="M10">
-        <v>0.9725811820548913</v>
+        <v>6.9086351900481419E-3</v>
       </c>
       <c r="N10">
-        <v>-0.42986328445585731</v>
+        <v>0.7579728903750047</v>
       </c>
       <c r="O10">
-        <v>0.19693331425647789</v>
+        <v>0.1292768105668764</v>
       </c>
       <c r="P10" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="Q10">
-        <v>0.33448702010404929</v>
+        <v>7.5994987090529556E-2</v>
       </c>
       <c r="R10">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="S10">
-        <v>133073425</v>
+        <v>2128865</v>
       </c>
       <c r="T10" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="C11">
         <v>40</v>
       </c>
       <c r="D11">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="E11">
+        <v>12</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>6</v>
+      </c>
+      <c r="H11">
+        <v>3</v>
+      </c>
+      <c r="I11">
+        <v>3</v>
+      </c>
+      <c r="J11">
+        <v>-22.803341363151539</v>
+      </c>
+      <c r="K11">
+        <v>6.9086351900481419E-3</v>
+      </c>
+      <c r="N11">
+        <v>0.7579728903750047</v>
+      </c>
+      <c r="O11">
+        <v>0.1292768105668764</v>
+      </c>
+      <c r="P11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q11">
+        <v>7.5994987090529556E-2</v>
+      </c>
+      <c r="R11">
         <v>17</v>
       </c>
-      <c r="F11">
-        <v>20</v>
-      </c>
-      <c r="G11">
-        <v>18</v>
-      </c>
-      <c r="H11">
-        <v>17</v>
-      </c>
-      <c r="I11">
-        <v>2</v>
-      </c>
-      <c r="J11">
-        <v>-1.633196390048461</v>
-      </c>
-      <c r="K11">
-        <v>3.3720335007724478E-2</v>
-      </c>
-      <c r="L11">
-        <v>-1.134036057819958</v>
-      </c>
-      <c r="M11">
-        <v>0.19721566055727069</v>
-      </c>
-      <c r="N11">
-        <v>-4.8885893674578462E-2</v>
-      </c>
-      <c r="O11">
-        <v>0.16093896671938479</v>
-      </c>
-      <c r="P11" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q11">
-        <v>0.37092368508496931</v>
-      </c>
-      <c r="R11">
-        <v>6</v>
-      </c>
       <c r="S11">
-        <v>133073425</v>
+        <v>2128865</v>
       </c>
       <c r="T11" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.2">
@@ -1417,52 +1405,52 @@
         <v>26</v>
       </c>
       <c r="B12" t="s">
-        <v>94</v>
+        <v>41</v>
       </c>
       <c r="C12">
         <v>40</v>
       </c>
       <c r="D12">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="E12">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F12">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="G12">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="H12">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J12">
-        <v>19.9230123263353</v>
+        <v>-7.8321264046306016E-2</v>
       </c>
       <c r="K12">
-        <v>3.6247603352829387E-2</v>
+        <v>8.6503849923604253E-3</v>
       </c>
       <c r="L12">
-        <v>1.895096137558284</v>
+        <v>1.1581395121537949E-2</v>
       </c>
       <c r="M12">
-        <v>0.79271640286172551</v>
+        <v>0.72348059088520011</v>
       </c>
       <c r="N12">
-        <v>-0.45388621491595948</v>
+        <v>-3.409057496971778E-3</v>
       </c>
       <c r="O12">
-        <v>0.18413000494443749</v>
+        <v>1.389916755741271E-2</v>
       </c>
       <c r="P12" t="s">
         <v>22</v>
       </c>
       <c r="Q12">
-        <v>0.36247603352829388</v>
+        <v>9.5154234915964683E-2</v>
       </c>
       <c r="R12">
         <v>6</v>
@@ -1476,320 +1464,320 @@
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="C13">
         <v>40</v>
       </c>
       <c r="D13">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E13">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F13">
         <v>20</v>
       </c>
       <c r="G13">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="H13">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I13">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J13">
-        <v>-1.260038083591308E-2</v>
+        <v>6.9681561996779386</v>
       </c>
       <c r="K13">
-        <v>3.8529988286322092E-2</v>
+        <v>9.7050505421018649E-3</v>
       </c>
       <c r="L13">
-        <v>-9.3742665620836802E-4</v>
+        <v>4.0423483628556083</v>
       </c>
       <c r="M13">
-        <v>0.89173503949775013</v>
+        <v>0.23256834577617311</v>
       </c>
       <c r="N13">
-        <v>-4.5548806548771951E-4</v>
+        <v>0.28594337090713912</v>
       </c>
       <c r="O13">
-        <v>0.10147547488379829</v>
+        <v>4.4643533386898179E-2</v>
       </c>
       <c r="P13" t="s">
         <v>22</v>
       </c>
       <c r="Q13">
-        <v>0.14191087827643159</v>
+        <v>0.1067555559631205</v>
       </c>
       <c r="R13">
         <v>6</v>
       </c>
       <c r="S13">
-        <v>133073425</v>
+        <v>13284922</v>
       </c>
       <c r="T13" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C14">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="D14">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="E14">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F14">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="G14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H14">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J14">
-        <v>-11.21660759836565</v>
+        <v>6.9690650935216167</v>
       </c>
       <c r="K14">
-        <v>4.2135399271503018E-2</v>
+        <v>9.8479194469968979E-3</v>
       </c>
       <c r="L14">
-        <v>8.0113320842457032</v>
+        <v>4.1271100169288548</v>
       </c>
       <c r="M14">
-        <v>8.2073645054145314E-2</v>
+        <v>0.2241431296334159</v>
       </c>
       <c r="N14">
-        <v>-5.579132711799388E-2</v>
+        <v>0.28423267888847598</v>
       </c>
       <c r="O14">
-        <v>0.77830569067477429</v>
+        <v>4.6332584222416762E-2</v>
       </c>
       <c r="P14" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="Q14">
-        <v>0.42135399271503021</v>
+        <v>0.10832711391696589</v>
       </c>
       <c r="R14">
         <v>6</v>
       </c>
       <c r="S14">
-        <v>133073425</v>
+        <v>13284922</v>
       </c>
       <c r="T14" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>108</v>
+        <v>44</v>
       </c>
       <c r="C15">
         <v>40</v>
       </c>
       <c r="D15">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E15">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F15">
         <v>20</v>
       </c>
       <c r="G15">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="H15">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I15">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J15">
-        <v>-0.64182551778097552</v>
+        <v>7.1381178000743226</v>
       </c>
       <c r="K15">
-        <v>4.4623548675940997E-2</v>
+        <v>9.8480153092416426E-3</v>
       </c>
       <c r="L15">
-        <v>-0.67899955839014736</v>
+        <v>4.329714480366655</v>
       </c>
       <c r="M15">
-        <v>6.7666380951470359E-2</v>
+        <v>0.21334116590455501</v>
       </c>
       <c r="N15">
-        <v>-2.978751349915873E-2</v>
+        <v>0.29426947850860902</v>
       </c>
       <c r="O15">
-        <v>4.3910887462403618E-2</v>
+        <v>4.4148558293154373E-2</v>
       </c>
       <c r="P15" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="Q15">
-        <v>0.28107287101966988</v>
+        <v>0.1083281684016581</v>
       </c>
       <c r="R15">
         <v>6</v>
       </c>
       <c r="S15">
-        <v>133073425</v>
+        <v>13284922</v>
       </c>
       <c r="T15" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="C16">
         <v>40</v>
       </c>
       <c r="D16">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E16">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F16">
         <v>20</v>
       </c>
       <c r="G16">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H16">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J16">
-        <v>0.11859871478295581</v>
+        <v>7.1381178000743226</v>
       </c>
       <c r="K16">
-        <v>1.100281756132389E-2</v>
+        <v>9.8480153092416426E-3</v>
       </c>
       <c r="L16">
-        <v>0.1236640445750682</v>
+        <v>4.329714480366655</v>
       </c>
       <c r="M16">
-        <v>4.5031555842553472E-2</v>
+        <v>0.21334116590455501</v>
       </c>
       <c r="N16">
-        <v>-1.1503664062220129E-3</v>
+        <v>0.29426947850860902</v>
       </c>
       <c r="O16">
-        <v>0.62111587167777627</v>
+        <v>4.4148558293154373E-2</v>
       </c>
       <c r="P16" t="s">
         <v>22</v>
       </c>
       <c r="Q16">
-        <v>6.0515496587281413E-2</v>
+        <v>0.1083281684016581</v>
       </c>
       <c r="R16">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="S16">
-        <v>89522747</v>
+        <v>13284922</v>
       </c>
       <c r="T16" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="B17" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="C17">
         <v>40</v>
       </c>
       <c r="D17">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E17">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F17">
         <v>20</v>
       </c>
       <c r="G17">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="H17">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I17">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J17">
-        <v>1.700693370018945E-3</v>
+        <v>-0.2036002241316634</v>
       </c>
       <c r="K17">
-        <v>1.6527650890068541E-2</v>
+        <v>1.023784786689722E-2</v>
       </c>
       <c r="L17">
-        <v>1.7273509915702681E-3</v>
+        <v>0.169482382798293</v>
       </c>
       <c r="M17">
-        <v>6.5873717468422646E-2</v>
+        <v>5.8723928208935447E-2</v>
       </c>
       <c r="N17">
-        <v>-2.869657691070538E-5</v>
+        <v>-2.8484723019942941E-3</v>
       </c>
       <c r="O17">
-        <v>0.42167129786056079</v>
+        <v>0.42046138787926468</v>
       </c>
       <c r="P17" t="s">
         <v>22</v>
       </c>
       <c r="Q17">
-        <v>9.0902079895376978E-2</v>
+        <v>0.11261632653586939</v>
       </c>
       <c r="R17">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="S17">
-        <v>89522747</v>
+        <v>133073425</v>
       </c>
       <c r="T17" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="C18">
         <v>40</v>
@@ -1804,125 +1792,125 @@
         <v>20</v>
       </c>
       <c r="G18">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="H18">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="I18">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J18">
-        <v>-0.43652211470167579</v>
+        <v>-4.0130514757324862</v>
       </c>
       <c r="K18">
-        <v>2.2217947542258091E-2</v>
+        <v>1.047870001632694E-2</v>
       </c>
       <c r="L18">
-        <v>-0.19208537984950011</v>
+        <v>-2.457130685960335</v>
       </c>
       <c r="M18">
-        <v>0.43918604022582541</v>
+        <v>1.8990177697616881E-2</v>
       </c>
       <c r="N18">
-        <v>-5.190079658953144E-3</v>
+        <v>6.1737799047181748E-2</v>
       </c>
       <c r="O18">
-        <v>0.58962557762149759</v>
+        <v>0.13416257351562119</v>
       </c>
       <c r="P18" t="s">
         <v>22</v>
       </c>
       <c r="Q18">
-        <v>0.24439742296483899</v>
+        <v>0.11526570017959641</v>
       </c>
       <c r="R18">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="S18">
-        <v>89522747</v>
+        <v>121821143</v>
       </c>
       <c r="T18" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C19">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="D19">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="E19">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F19">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="G19">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H19">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J19">
-        <v>7.2695508233836668</v>
+        <v>6.8723120277468226</v>
       </c>
       <c r="K19">
-        <v>2.351559916446128E-2</v>
+        <v>1.060043060018972E-2</v>
       </c>
       <c r="L19">
-        <v>-1.263032102351612</v>
+        <v>3.86396155910648</v>
       </c>
       <c r="M19">
-        <v>0.60933461171166714</v>
+        <v>0.25304369152907619</v>
       </c>
       <c r="N19">
-        <v>-5.0509408573442362E-2</v>
+        <v>0.27866086543622792</v>
       </c>
       <c r="O19">
-        <v>0.58307674362554818</v>
+        <v>4.9869561746215367E-2</v>
       </c>
       <c r="P19" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="Q19">
-        <v>0.11757799582230639</v>
+        <v>0.11660473660208689</v>
       </c>
       <c r="R19">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="S19">
-        <v>89522747</v>
+        <v>13284922</v>
       </c>
       <c r="T19" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C20">
         <v>40</v>
       </c>
       <c r="D20">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E20">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F20">
         <v>20</v>
@@ -1931,43 +1919,43 @@
         <v>10</v>
       </c>
       <c r="H20">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J20">
-        <v>3.3725483975789963E-2</v>
+        <v>6.8723120277468226</v>
       </c>
       <c r="K20">
-        <v>3.5040603635048143E-2</v>
+        <v>1.060043060018972E-2</v>
       </c>
       <c r="L20">
-        <v>-1.152498033453846E-2</v>
+        <v>3.86396155910648</v>
       </c>
       <c r="M20">
-        <v>0.57765486833769542</v>
+        <v>0.25304369152907619</v>
       </c>
       <c r="N20">
-        <v>-6.0331087566292099E-4</v>
+        <v>0.27866086543622792</v>
       </c>
       <c r="O20">
-        <v>0.45559455732237808</v>
+        <v>4.9869561746215367E-2</v>
       </c>
       <c r="P20" t="s">
         <v>22</v>
       </c>
       <c r="Q20">
-        <v>0.1886824812491586</v>
+        <v>0.11660473660208689</v>
       </c>
       <c r="R20">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="S20">
-        <v>89522747</v>
+        <v>13284922</v>
       </c>
       <c r="T20" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.2">
@@ -1975,7 +1963,7 @@
         <v>50</v>
       </c>
       <c r="B21" t="s">
-        <v>93</v>
+        <v>22</v>
       </c>
       <c r="C21">
         <v>40</v>
@@ -1999,28 +1987,28 @@
         <v>6</v>
       </c>
       <c r="J21">
-        <v>3.1070396841110771E-2</v>
+        <v>0.11859871478295581</v>
       </c>
       <c r="K21">
-        <v>3.5724564605321821E-2</v>
+        <v>1.100281756132389E-2</v>
       </c>
       <c r="L21">
-        <v>1.472575294793871E-2</v>
+        <v>0.1236640445750682</v>
       </c>
       <c r="M21">
-        <v>0.44700657425670159</v>
+        <v>4.5031555842553472E-2</v>
       </c>
       <c r="N21">
-        <v>-6.9378304763142778E-4</v>
+        <v>-1.1503664062220129E-3</v>
       </c>
       <c r="O21">
-        <v>0.35735323418254311</v>
+        <v>0.62111587167777627</v>
       </c>
       <c r="P21" t="s">
         <v>22</v>
       </c>
       <c r="Q21">
-        <v>0.39297021065853999</v>
+        <v>6.0515496587281413E-2</v>
       </c>
       <c r="R21">
         <v>16</v>
@@ -2034,10 +2022,10 @@
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="B22" t="s">
-        <v>101</v>
+        <v>52</v>
       </c>
       <c r="C22">
         <v>40</v>
@@ -2052,54 +2040,54 @@
         <v>20</v>
       </c>
       <c r="G22">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="H22">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I22">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J22">
-        <v>-0.20260574613204471</v>
+        <v>-0.1331189176788026</v>
       </c>
       <c r="K22">
-        <v>4.0443435827340349E-2</v>
+        <v>1.1016011494016729E-2</v>
       </c>
       <c r="L22">
-        <v>0.20020978373367571</v>
+        <v>0.1506252201867532</v>
       </c>
       <c r="M22">
-        <v>0.12755201420324741</v>
+        <v>1.35913743220105E-2</v>
       </c>
       <c r="N22">
-        <v>-6.3686101042650467E-4</v>
+        <v>-4.052326142109844E-3</v>
       </c>
       <c r="O22">
-        <v>0.89891539428242662</v>
+        <v>8.5410763737419237E-2</v>
       </c>
       <c r="P22" t="s">
         <v>22</v>
       </c>
       <c r="Q22">
-        <v>0.37470157170695279</v>
+        <v>0.1211761264341841</v>
       </c>
       <c r="R22">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="S22">
-        <v>89522747</v>
+        <v>133073425</v>
       </c>
       <c r="T22" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="B23" t="s">
-        <v>103</v>
+        <v>53</v>
       </c>
       <c r="C23">
         <v>40</v>
@@ -2114,232 +2102,232 @@
         <v>20</v>
       </c>
       <c r="G23">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="H23">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I23">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J23">
-        <v>-1.4459036074786811</v>
+        <v>-1.982562158167456</v>
       </c>
       <c r="K23">
-        <v>4.0542723384057462E-2</v>
+        <v>1.170929601608142E-2</v>
       </c>
       <c r="L23">
-        <v>1.4400158682288371</v>
+        <v>-1.200690089334536</v>
       </c>
       <c r="M23">
-        <v>0.1248867679914118</v>
+        <v>0.1760500357135035</v>
       </c>
       <c r="N23">
-        <v>-4.5906516239240438E-3</v>
+        <v>-6.2295022081060088E-2</v>
       </c>
       <c r="O23">
-        <v>0.89795903610099603</v>
+        <v>7.8871703667559523E-2</v>
       </c>
       <c r="P23" t="s">
         <v>22</v>
       </c>
       <c r="Q23">
-        <v>0.38425609714036352</v>
+        <v>0.12880225617689561</v>
       </c>
       <c r="R23">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="S23">
-        <v>89522747</v>
+        <v>133073425</v>
       </c>
       <c r="T23" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="B24" t="s">
-        <v>104</v>
+        <v>54</v>
       </c>
       <c r="C24">
         <v>40</v>
       </c>
       <c r="D24">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E24">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F24">
         <v>20</v>
       </c>
       <c r="G24">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="H24">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I24">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J24">
-        <v>-0.82333361080917555</v>
+        <v>-4.750300229395929E-2</v>
       </c>
       <c r="K24">
-        <v>4.0542723438265302E-2</v>
+        <v>1.182244492197717E-2</v>
       </c>
       <c r="L24">
-        <v>0.81998098654543516</v>
+        <v>-5.9297576250654837E-5</v>
       </c>
       <c r="M24">
-        <v>0.124886767452096</v>
+        <v>0.99772319308620461</v>
       </c>
       <c r="N24">
-        <v>-2.614031648958624E-3</v>
+        <v>-1.612938888258437E-3</v>
       </c>
       <c r="O24">
-        <v>0.89795903575976854</v>
+        <v>6.1507301934860092E-2</v>
       </c>
       <c r="P24" t="s">
         <v>22</v>
       </c>
       <c r="Q24">
-        <v>0.38425609630441437</v>
+        <v>0.13004689414174889</v>
       </c>
       <c r="R24">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="S24">
-        <v>89522747</v>
+        <v>133073425</v>
       </c>
       <c r="T24" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="B25" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C25">
         <v>40</v>
       </c>
       <c r="D25">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="E25">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F25">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="G25">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H25">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="I25">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J25">
-        <v>1.802877254547621</v>
+        <v>2.934218140550806E-2</v>
       </c>
       <c r="K25">
-        <v>4.5166804094122083E-2</v>
+        <v>1.233786693594505E-2</v>
       </c>
       <c r="L25">
-        <v>-4.4303820204361672</v>
+        <v>5.8009441696275928E-2</v>
       </c>
       <c r="M25">
-        <v>3.7034618687144618E-4</v>
+        <v>7.2567968168353956E-3</v>
       </c>
       <c r="N25">
-        <v>2.693100153898613E-2</v>
+        <v>-6.4529169307323768E-4</v>
       </c>
       <c r="O25">
-        <v>0.55291929856072264</v>
+        <v>0.2925022218747505</v>
       </c>
       <c r="P25" t="s">
         <v>22</v>
       </c>
       <c r="Q25">
-        <v>0.49683484503534281</v>
+        <v>0.12337866935945049</v>
       </c>
       <c r="R25">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S25">
-        <v>89522747</v>
+        <v>2128865</v>
       </c>
       <c r="T25" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="B26" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C26">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="D26">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="E26">
+        <v>6</v>
+      </c>
+      <c r="F26">
+        <v>6</v>
+      </c>
+      <c r="G26">
+        <v>5</v>
+      </c>
+      <c r="H26">
+        <v>4</v>
+      </c>
+      <c r="I26">
+        <v>3</v>
+      </c>
+      <c r="J26">
+        <v>2.934218140550806E-2</v>
+      </c>
+      <c r="K26">
+        <v>1.233786693594505E-2</v>
+      </c>
+      <c r="L26">
+        <v>5.8009441696275928E-2</v>
+      </c>
+      <c r="M26">
+        <v>7.2567968168353956E-3</v>
+      </c>
+      <c r="N26">
+        <v>-6.4529169307323768E-4</v>
+      </c>
+      <c r="O26">
+        <v>0.2925022218747505</v>
+      </c>
+      <c r="P26" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q26">
+        <v>0.12337866935945049</v>
+      </c>
+      <c r="R26">
         <v>17</v>
       </c>
-      <c r="F26">
-        <v>20</v>
-      </c>
-      <c r="G26">
-        <v>9</v>
-      </c>
-      <c r="H26">
-        <v>20</v>
-      </c>
-      <c r="I26">
-        <v>8</v>
-      </c>
-      <c r="J26">
-        <v>-1.6259321142582519E-2</v>
-      </c>
-      <c r="K26">
-        <v>8.568065626575629E-4</v>
-      </c>
-      <c r="L26">
-        <v>-6.6664480117853446E-3</v>
-      </c>
-      <c r="M26">
-        <v>0.26562208591984687</v>
-      </c>
-      <c r="N26">
-        <v>-4.9512265248954869E-4</v>
-      </c>
-      <c r="O26">
-        <v>4.4754234391201783E-2</v>
-      </c>
-      <c r="P26" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q26">
-        <v>9.4248721892331924E-3</v>
-      </c>
-      <c r="R26">
-        <v>6</v>
-      </c>
       <c r="S26">
-        <v>13284922</v>
+        <v>2128865</v>
       </c>
       <c r="T26" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.2">
@@ -2347,52 +2335,52 @@
         <v>20</v>
       </c>
       <c r="B27" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="C27">
         <v>40</v>
       </c>
       <c r="D27">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E27">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F27">
         <v>20</v>
       </c>
       <c r="G27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H27">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I27">
         <v>8</v>
       </c>
       <c r="J27">
-        <v>-1.095546499963147</v>
+        <v>8.778219063545146</v>
       </c>
       <c r="K27">
-        <v>9.1975840020432531E-4</v>
+        <v>1.254613265669078E-2</v>
       </c>
       <c r="L27">
-        <v>-0.41315654599708468</v>
+        <v>2.4767140468227491</v>
       </c>
       <c r="M27">
-        <v>0.30851175888574051</v>
+        <v>0.57344882536354624</v>
       </c>
       <c r="N27">
-        <v>-2.733741813760043E-2</v>
+        <v>0.71498745819398024</v>
       </c>
       <c r="O27">
-        <v>9.8981671127009827E-2</v>
+        <v>3.2591176058353969E-4</v>
       </c>
       <c r="P27" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="Q27">
-        <v>1.011734240224758E-2</v>
+        <v>0.13800745922359861</v>
       </c>
       <c r="R27">
         <v>6</v>
@@ -2406,10 +2394,10 @@
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="C28">
         <v>40</v>
@@ -2424,46 +2412,46 @@
         <v>20</v>
       </c>
       <c r="G28">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="H28">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I28">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J28">
-        <v>-0.14205413296616129</v>
+        <v>-4.6352608530592893E-2</v>
       </c>
       <c r="K28">
-        <v>2.081624073858525E-3</v>
+        <v>1.2633176341423E-2</v>
       </c>
       <c r="L28">
-        <v>9.4352205965898842E-2</v>
+        <v>3.2440671343286917E-2</v>
       </c>
       <c r="M28">
-        <v>0.1040460824239669</v>
+        <v>0.12384303283971571</v>
       </c>
       <c r="N28">
-        <v>-4.1054188763062988E-3</v>
+        <v>-1.3848172371075751E-3</v>
       </c>
       <c r="O28">
-        <v>8.0312127033090708E-2</v>
+        <v>9.7775863025042806E-2</v>
       </c>
       <c r="P28" t="s">
         <v>22</v>
       </c>
       <c r="Q28">
-        <v>2.2897864812443769E-2</v>
+        <v>0.13896493975565299</v>
       </c>
       <c r="R28">
         <v>6</v>
       </c>
       <c r="S28">
-        <v>13284922</v>
+        <v>133073425</v>
       </c>
       <c r="T28" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.2">
@@ -2471,52 +2459,52 @@
         <v>20</v>
       </c>
       <c r="B29" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="C29">
         <v>40</v>
       </c>
       <c r="D29">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E29">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F29">
         <v>20</v>
       </c>
       <c r="G29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H29">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I29">
         <v>8</v>
       </c>
       <c r="J29">
-        <v>-2.073018440140515E-3</v>
+        <v>8.7580608200173398</v>
       </c>
       <c r="K29">
-        <v>3.1492180990437459E-3</v>
+        <v>1.294701122001663E-2</v>
       </c>
       <c r="L29">
-        <v>1.304024876802637E-3</v>
+        <v>2.490322267641115</v>
       </c>
       <c r="M29">
-        <v>0.1407043601238136</v>
+        <v>0.57234500889163198</v>
       </c>
       <c r="N29">
-        <v>-7.1615803903430991E-5</v>
+        <v>0.71630176720756444</v>
       </c>
       <c r="O29">
-        <v>4.7726814047783311E-2</v>
+        <v>3.2876526991895488E-4</v>
       </c>
       <c r="P29" t="s">
         <v>22</v>
       </c>
       <c r="Q29">
-        <v>3.4641399089481197E-2</v>
+        <v>0.14241712342018301</v>
       </c>
       <c r="R29">
         <v>6</v>
@@ -2530,64 +2518,64 @@
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="C30">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="D30">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="E30">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="F30">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="G30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H30">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="I30">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J30">
-        <v>6.9681561996779386</v>
+        <v>-6.4397121541658073</v>
       </c>
       <c r="K30">
-        <v>9.7050505421018649E-3</v>
+        <v>1.5464084997444279E-2</v>
       </c>
       <c r="L30">
-        <v>4.0423483628556083</v>
+        <v>-2.8219310822468748</v>
       </c>
       <c r="M30">
-        <v>0.23256834577617311</v>
+        <v>0.25055043391974419</v>
       </c>
       <c r="N30">
-        <v>0.28594337090713912</v>
+        <v>-8.6833695823865936E-2</v>
       </c>
       <c r="O30">
-        <v>4.4643533386898179E-2</v>
+        <v>0.32965826370762719</v>
       </c>
       <c r="P30" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="Q30">
-        <v>0.1067555559631205</v>
+        <v>0.11757799582230639</v>
       </c>
       <c r="R30">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="S30">
-        <v>13284922</v>
+        <v>42607288</v>
       </c>
       <c r="T30" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.2">
@@ -2595,52 +2583,52 @@
         <v>20</v>
       </c>
       <c r="B31" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="C31">
         <v>40</v>
       </c>
       <c r="D31">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="E31">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="F31">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="G31">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H31">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="I31">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J31">
-        <v>6.9690650935216167</v>
+        <v>-43.287102228261197</v>
       </c>
       <c r="K31">
-        <v>9.8479194469968979E-3</v>
+        <v>1.5477414766989561E-2</v>
       </c>
       <c r="L31">
-        <v>4.1271100169288548</v>
+        <v>32.242329972467118</v>
       </c>
       <c r="M31">
-        <v>0.2241431296334159</v>
+        <v>0.11066321959813701</v>
       </c>
       <c r="N31">
-        <v>0.28423267888847598</v>
+        <v>-0.75659548551375977</v>
       </c>
       <c r="O31">
-        <v>4.6332584222416762E-2</v>
+        <v>0.3303325748257207</v>
       </c>
       <c r="P31" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="Q31">
-        <v>0.10832711391696589</v>
+        <v>0.15477414766989561</v>
       </c>
       <c r="R31">
         <v>6</v>
@@ -2657,52 +2645,46 @@
         <v>20</v>
       </c>
       <c r="B32" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="C32">
         <v>40</v>
       </c>
       <c r="D32">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="E32">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F32">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G32">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H32">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="I32">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J32">
-        <v>7.1381178000743226</v>
+        <v>9.1883088869715284</v>
       </c>
       <c r="K32">
-        <v>9.8480153092416426E-3</v>
-      </c>
-      <c r="L32">
-        <v>4.329714480366655</v>
-      </c>
-      <c r="M32">
-        <v>0.21334116590455501</v>
+        <v>1.6114603451952848E-2</v>
       </c>
       <c r="N32">
-        <v>0.29426947850860902</v>
+        <v>0.39369268594378731</v>
       </c>
       <c r="O32">
-        <v>4.4148558293154373E-2</v>
+        <v>6.7693575312681289E-2</v>
       </c>
       <c r="P32" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="Q32">
-        <v>0.1083281684016581</v>
+        <v>0.17726063797148139</v>
       </c>
       <c r="R32">
         <v>6</v>
@@ -2716,64 +2698,64 @@
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="B33" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="C33">
         <v>40</v>
       </c>
       <c r="D33">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E33">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F33">
         <v>20</v>
       </c>
       <c r="G33">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H33">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I33">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J33">
-        <v>7.1381178000743226</v>
+        <v>1.700693370018945E-3</v>
       </c>
       <c r="K33">
-        <v>9.8480153092416426E-3</v>
+        <v>1.6527650890068541E-2</v>
       </c>
       <c r="L33">
-        <v>4.329714480366655</v>
+        <v>1.7273509915702681E-3</v>
       </c>
       <c r="M33">
-        <v>0.21334116590455501</v>
+        <v>6.5873717468422646E-2</v>
       </c>
       <c r="N33">
-        <v>0.29426947850860902</v>
+        <v>-2.869657691070538E-5</v>
       </c>
       <c r="O33">
-        <v>4.4148558293154373E-2</v>
+        <v>0.42167129786056079</v>
       </c>
       <c r="P33" t="s">
         <v>22</v>
       </c>
       <c r="Q33">
-        <v>0.1083281684016581</v>
+        <v>9.0902079895376978E-2</v>
       </c>
       <c r="R33">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="S33">
-        <v>13284922</v>
+        <v>89522747</v>
       </c>
       <c r="T33" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.2">
@@ -2781,52 +2763,52 @@
         <v>20</v>
       </c>
       <c r="B34" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="C34">
         <v>40</v>
       </c>
       <c r="D34">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E34">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F34">
         <v>20</v>
       </c>
       <c r="G34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H34">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I34">
         <v>8</v>
       </c>
       <c r="J34">
-        <v>6.8723120277468226</v>
+        <v>-2.1230025273842492</v>
       </c>
       <c r="K34">
-        <v>1.060043060018972E-2</v>
+        <v>1.8064545201709799E-2</v>
       </c>
       <c r="L34">
-        <v>3.86396155910648</v>
+        <v>-4.2442395419746886</v>
       </c>
       <c r="M34">
-        <v>0.25304369152907619</v>
+        <v>6.8631985310142957E-4</v>
       </c>
       <c r="N34">
-        <v>0.27866086543622792</v>
+        <v>-0.2126802214079678</v>
       </c>
       <c r="O34">
-        <v>4.9869561746215367E-2</v>
+        <v>5.045211617481182E-5</v>
       </c>
       <c r="P34" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="Q34">
-        <v>0.11660473660208689</v>
+        <v>0.1987099972188078</v>
       </c>
       <c r="R34">
         <v>6</v>
@@ -2840,624 +2822,630 @@
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="C35">
         <v>40</v>
       </c>
       <c r="D35">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="E35">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="F35">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="G35">
         <v>10</v>
       </c>
       <c r="H35">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="I35">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J35">
-        <v>6.8723120277468226</v>
+        <v>-12.263010912480521</v>
       </c>
       <c r="K35">
-        <v>1.060043060018972E-2</v>
+        <v>1.878230462299495E-2</v>
       </c>
       <c r="L35">
-        <v>3.86396155910648</v>
+        <v>2.9137970146023302</v>
       </c>
       <c r="M35">
-        <v>0.25304369152907619</v>
+        <v>0.46661628770213909</v>
       </c>
       <c r="N35">
-        <v>0.27866086543622792</v>
+        <v>-0.2199971736394063</v>
       </c>
       <c r="O35">
-        <v>4.9869561746215367E-2</v>
+        <v>0.14488849165586709</v>
       </c>
       <c r="P35" t="s">
         <v>22</v>
       </c>
       <c r="Q35">
-        <v>0.11660473660208689</v>
+        <v>0.1878230462299495</v>
       </c>
       <c r="R35">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S35">
-        <v>13284922</v>
+        <v>121821143</v>
       </c>
       <c r="T35" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="B36" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C36">
         <v>40</v>
       </c>
       <c r="D36">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E36">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F36">
         <v>20</v>
       </c>
       <c r="G36">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H36">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I36">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J36">
-        <v>8.778219063545146</v>
+        <v>-0.43652211470167579</v>
       </c>
       <c r="K36">
-        <v>1.254613265669078E-2</v>
+        <v>2.2217947542258091E-2</v>
       </c>
       <c r="L36">
-        <v>2.4767140468227491</v>
+        <v>-0.19208537984950011</v>
       </c>
       <c r="M36">
-        <v>0.57344882536354624</v>
+        <v>0.43918604022582541</v>
       </c>
       <c r="N36">
-        <v>0.71498745819398024</v>
+        <v>-5.190079658953144E-3</v>
       </c>
       <c r="O36">
-        <v>3.2591176058353969E-4</v>
+        <v>0.58962557762149759</v>
       </c>
       <c r="P36" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="Q36">
-        <v>0.13800745922359861</v>
+        <v>0.24439742296483899</v>
       </c>
       <c r="R36">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="S36">
-        <v>13284922</v>
+        <v>89522747</v>
       </c>
       <c r="T36" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="B37" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C37">
         <v>40</v>
       </c>
       <c r="D37">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E37">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F37">
         <v>20</v>
       </c>
       <c r="G37">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="H37">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="I37">
+        <v>1</v>
+      </c>
+      <c r="J37">
+        <v>12.7733473445151</v>
+      </c>
+      <c r="K37">
+        <v>2.336455351576475E-2</v>
+      </c>
+      <c r="L37">
+        <v>-1.018318786815763</v>
+      </c>
+      <c r="M37">
+        <v>0.77655184377872344</v>
+      </c>
+      <c r="N37">
+        <v>0.27412292260469179</v>
+      </c>
+      <c r="O37">
+        <v>5.3514792056003201E-2</v>
+      </c>
+      <c r="P37" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q37">
+        <v>0.2570100886734123</v>
+      </c>
+      <c r="R37">
         <v>8</v>
       </c>
-      <c r="J37">
-        <v>8.7580608200173398</v>
-      </c>
-      <c r="K37">
-        <v>1.294701122001663E-2</v>
-      </c>
-      <c r="L37">
-        <v>2.490322267641115</v>
-      </c>
-      <c r="M37">
-        <v>0.57234500889163198</v>
-      </c>
-      <c r="N37">
-        <v>0.71630176720756444</v>
-      </c>
-      <c r="O37">
-        <v>3.2876526991895488E-4</v>
-      </c>
-      <c r="P37" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q37">
-        <v>0.14241712342018301</v>
-      </c>
-      <c r="R37">
-        <v>6</v>
-      </c>
       <c r="S37">
-        <v>13284922</v>
+        <v>11663173</v>
       </c>
       <c r="T37" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="B38" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C38">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="D38">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E38">
         <v>7</v>
       </c>
       <c r="F38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H38">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I38">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J38">
-        <v>-43.287102228261197</v>
+        <v>7.2695508233836668</v>
       </c>
       <c r="K38">
-        <v>1.5477414766989561E-2</v>
+        <v>2.351559916446128E-2</v>
       </c>
       <c r="L38">
-        <v>32.242329972467118</v>
+        <v>-1.263032102351612</v>
       </c>
       <c r="M38">
-        <v>0.11066321959813701</v>
+        <v>0.60933461171166714</v>
       </c>
       <c r="N38">
-        <v>-0.75659548551375977</v>
+        <v>-5.0509408573442362E-2</v>
       </c>
       <c r="O38">
-        <v>0.3303325748257207</v>
+        <v>0.58307674362554818</v>
       </c>
       <c r="P38" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="Q38">
-        <v>0.15477414766989561</v>
+        <v>0.11757799582230639</v>
       </c>
       <c r="R38">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="S38">
-        <v>13284922</v>
+        <v>89522747</v>
       </c>
       <c r="T38" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="B39" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="C39">
         <v>40</v>
       </c>
       <c r="D39">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E39">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H39">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I39">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J39">
-        <v>9.1883088869715284</v>
+        <v>7.5363006307403229E-3</v>
       </c>
       <c r="K39">
-        <v>1.6114603451952848E-2</v>
+        <v>2.495465211544555E-2</v>
+      </c>
+      <c r="L39">
+        <v>7.1933968130938851E-3</v>
+      </c>
+      <c r="M39">
+        <v>0.17782997038347961</v>
       </c>
       <c r="N39">
-        <v>0.39369268594378731</v>
+        <v>-9.4674345676398091E-5</v>
       </c>
       <c r="O39">
-        <v>6.7693575312681289E-2</v>
+        <v>0.59658396360251675</v>
       </c>
       <c r="P39" t="s">
         <v>22</v>
       </c>
       <c r="Q39">
-        <v>0.17726063797148139</v>
+        <v>0.13376644562604151</v>
       </c>
       <c r="R39">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="S39">
-        <v>13284922</v>
+        <v>2128865</v>
       </c>
       <c r="T39" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="B40" t="s">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="C40">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="D40">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="E40">
+        <v>6</v>
+      </c>
+      <c r="F40">
+        <v>6</v>
+      </c>
+      <c r="G40">
+        <v>5</v>
+      </c>
+      <c r="H40">
+        <v>4</v>
+      </c>
+      <c r="I40">
+        <v>3</v>
+      </c>
+      <c r="J40">
+        <v>7.5363006307403229E-3</v>
+      </c>
+      <c r="K40">
+        <v>2.495465211544555E-2</v>
+      </c>
+      <c r="L40">
+        <v>7.1933968130938851E-3</v>
+      </c>
+      <c r="M40">
+        <v>0.17782997038347961</v>
+      </c>
+      <c r="N40">
+        <v>-9.4674345676398091E-5</v>
+      </c>
+      <c r="O40">
+        <v>0.59658396360251675</v>
+      </c>
+      <c r="P40" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q40">
+        <v>0.13376644562604151</v>
+      </c>
+      <c r="R40">
         <v>17</v>
       </c>
-      <c r="F40">
-        <v>20</v>
-      </c>
-      <c r="G40">
-        <v>9</v>
-      </c>
-      <c r="H40">
-        <v>20</v>
-      </c>
-      <c r="I40">
-        <v>8</v>
-      </c>
-      <c r="J40">
-        <v>-2.1230025273842492</v>
-      </c>
-      <c r="K40">
-        <v>1.8064545201709799E-2</v>
-      </c>
-      <c r="L40">
-        <v>-4.2442395419746886</v>
-      </c>
-      <c r="M40">
-        <v>6.8631985310142957E-4</v>
-      </c>
-      <c r="N40">
-        <v>-0.2126802214079678</v>
-      </c>
-      <c r="O40">
-        <v>5.045211617481182E-5</v>
-      </c>
-      <c r="P40" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q40">
-        <v>0.1987099972188078</v>
-      </c>
-      <c r="R40">
-        <v>6</v>
-      </c>
       <c r="S40">
-        <v>13284922</v>
+        <v>2128865</v>
       </c>
       <c r="T40" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="B41" t="s">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="C41">
         <v>40</v>
       </c>
       <c r="D41">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E41">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F41">
         <v>20</v>
       </c>
       <c r="G41">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="H41">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="I41">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J41">
-        <v>2.3600169437746192E-15</v>
+        <v>2.702782975910396E-2</v>
       </c>
       <c r="K41">
-        <v>4.0259336436489872E-2</v>
+        <v>2.5083651135668919E-2</v>
       </c>
       <c r="L41">
-        <v>-2.0148961864054271E-15</v>
+        <v>2.255206296369511E-3</v>
       </c>
       <c r="M41">
-        <v>0.17241969897700229</v>
+        <v>0.88704585858769081</v>
       </c>
       <c r="N41">
-        <v>1</v>
+        <v>-8.0503850748489536E-4</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>0.19213886307957151</v>
       </c>
       <c r="P41" t="s">
         <v>22</v>
       </c>
       <c r="Q41">
-        <v>0.36667720331576908</v>
+        <v>0.19317208872234379</v>
       </c>
       <c r="R41">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="S41">
-        <v>13284922</v>
+        <v>46921566</v>
       </c>
       <c r="T41" t="s">
-        <v>23</v>
+        <v>72</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="B42" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C42">
         <v>40</v>
       </c>
       <c r="D42">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E42">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F42">
         <v>20</v>
       </c>
       <c r="G42">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="H42">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I42">
+        <v>1</v>
+      </c>
+      <c r="J42">
+        <v>12.30296935759703</v>
+      </c>
+      <c r="K42">
+        <v>2.5511422862639271E-2</v>
+      </c>
+      <c r="L42">
+        <v>-0.77550339143463309</v>
+      </c>
+      <c r="M42">
+        <v>0.82522015331433807</v>
+      </c>
+      <c r="N42">
+        <v>0.29611640722063881</v>
+      </c>
+      <c r="O42">
+        <v>3.4221852178898157E-2</v>
+      </c>
+      <c r="P42" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q42">
+        <v>0.28062565148903201</v>
+      </c>
+      <c r="R42">
         <v>8</v>
       </c>
-      <c r="J42">
-        <v>2.4132537111800582E-2</v>
-      </c>
-      <c r="K42">
-        <v>4.2642894750632231E-2</v>
-      </c>
-      <c r="L42">
-        <v>-7.375577523820686E-3</v>
-      </c>
-      <c r="M42">
-        <v>0.63057486905350801</v>
-      </c>
-      <c r="N42">
-        <v>-3.4607493422119111E-5</v>
-      </c>
-      <c r="O42">
-        <v>0.95528232059194007</v>
-      </c>
-      <c r="P42" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q42">
-        <v>0.19317208872234379</v>
-      </c>
-      <c r="R42">
-        <v>6</v>
-      </c>
       <c r="S42">
-        <v>13284922</v>
+        <v>11663173</v>
       </c>
       <c r="T42" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>20</v>
+        <v>74</v>
       </c>
       <c r="B43" t="s">
-        <v>110</v>
+        <v>69</v>
       </c>
       <c r="C43">
         <v>40</v>
       </c>
       <c r="D43">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="E43">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F43">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="G43">
         <v>10</v>
       </c>
       <c r="H43">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="I43">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J43">
-        <v>6.1393131425740251</v>
+        <v>-1.6899911440563228E-2</v>
       </c>
       <c r="K43">
-        <v>4.7232885865909388E-2</v>
+        <v>2.6753289125208302E-2</v>
       </c>
       <c r="L43">
-        <v>3.1811670589206789</v>
+        <v>9.1619112622529104E-3</v>
       </c>
       <c r="M43">
-        <v>0.41998463166520378</v>
+        <v>0.1154011911423645</v>
       </c>
       <c r="N43">
-        <v>0.57083849457037894</v>
+        <v>-4.8544115894937864E-6</v>
       </c>
       <c r="O43">
-        <v>1.1064646930455961E-3</v>
+        <v>0.97751959296810376</v>
       </c>
       <c r="P43" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="Q43">
-        <v>0.51956174452500326</v>
+        <v>0.13376644562604151</v>
       </c>
       <c r="R43">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="S43">
-        <v>13284922</v>
+        <v>118608625</v>
       </c>
       <c r="T43" t="s">
-        <v>23</v>
+        <v>75</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>20</v>
+        <v>74</v>
       </c>
       <c r="B44" t="s">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="C44">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="D44">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="E44">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F44">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="G44">
         <v>10</v>
       </c>
       <c r="H44">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="I44">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J44">
-        <v>6.1393131425740251</v>
+        <v>-1.6899911440563228E-2</v>
       </c>
       <c r="K44">
-        <v>4.7232885865909388E-2</v>
+        <v>2.6753289125208302E-2</v>
       </c>
       <c r="L44">
-        <v>3.1811670589206789</v>
+        <v>9.1619112622529104E-3</v>
       </c>
       <c r="M44">
-        <v>0.41998463166520378</v>
+        <v>0.1154011911423645</v>
       </c>
       <c r="N44">
-        <v>0.57083849457037894</v>
+        <v>-4.8544115894937864E-6</v>
       </c>
       <c r="O44">
-        <v>1.1064646930455961E-3</v>
+        <v>0.97751959296810376</v>
       </c>
       <c r="P44" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="Q44">
-        <v>0.51956174452500326</v>
+        <v>0.13376644562604151</v>
       </c>
       <c r="R44">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="S44">
-        <v>13284922</v>
+        <v>118608625</v>
       </c>
       <c r="T44" t="s">
-        <v>23</v>
+        <v>75</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="B45" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C45">
         <v>40</v>
@@ -3472,54 +3460,54 @@
         <v>6</v>
       </c>
       <c r="G45">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H45">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I45">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J45">
-        <v>-1.6899911440563228E-2</v>
+        <v>0.45692675160538382</v>
       </c>
       <c r="K45">
-        <v>2.6753289125208302E-2</v>
+        <v>2.9622600616636231E-2</v>
       </c>
       <c r="L45">
-        <v>9.1619112622529104E-3</v>
+        <v>0.48246825304111418</v>
       </c>
       <c r="M45">
-        <v>0.1154011911423645</v>
+        <v>0.15538786435449359</v>
       </c>
       <c r="N45">
-        <v>-4.8544115894937864E-6</v>
+        <v>-7.903944870596322E-3</v>
       </c>
       <c r="O45">
-        <v>0.97751959296810376</v>
+        <v>0.48714814763011799</v>
       </c>
       <c r="P45" t="s">
         <v>22</v>
       </c>
       <c r="Q45">
-        <v>0.13376644562604151</v>
+        <v>0.17213690282538999</v>
       </c>
       <c r="R45">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="S45">
-        <v>118608625</v>
+        <v>2128865</v>
       </c>
       <c r="T45" t="s">
-        <v>75</v>
+        <v>31</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="B46" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C46">
         <v>14</v>
@@ -3534,240 +3522,240 @@
         <v>6</v>
       </c>
       <c r="G46">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H46">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I46">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J46">
-        <v>-1.6899911440563228E-2</v>
+        <v>0.45692675160538382</v>
       </c>
       <c r="K46">
-        <v>2.6753289125208302E-2</v>
+        <v>2.9622600616636231E-2</v>
       </c>
       <c r="L46">
-        <v>9.1619112622529104E-3</v>
+        <v>0.48246825304111418</v>
       </c>
       <c r="M46">
-        <v>0.1154011911423645</v>
+        <v>0.15538786435449359</v>
       </c>
       <c r="N46">
-        <v>-4.8544115894937864E-6</v>
+        <v>-7.903944870596322E-3</v>
       </c>
       <c r="O46">
-        <v>0.97751959296810376</v>
+        <v>0.48714814763011799</v>
       </c>
       <c r="P46" t="s">
         <v>56</v>
       </c>
       <c r="Q46">
-        <v>0.13376644562604151</v>
+        <v>0.17213690282538999</v>
       </c>
       <c r="R46">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="S46">
-        <v>118608625</v>
+        <v>2128865</v>
       </c>
       <c r="T46" t="s">
-        <v>75</v>
+        <v>31</v>
       </c>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="B47" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="C47">
         <v>40</v>
       </c>
       <c r="D47">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="E47">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="F47">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="G47">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="H47">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I47">
         <v>0</v>
       </c>
       <c r="J47">
-        <v>-0.82706409565323469</v>
+        <v>-12.517542184017829</v>
       </c>
       <c r="K47">
-        <v>3.3819083490744882E-2</v>
+        <v>3.0191759373752711E-2</v>
       </c>
       <c r="L47">
-        <v>-0.75586117082043991</v>
+        <v>-0.48984399872651319</v>
       </c>
       <c r="M47">
-        <v>2.8055946343789721E-2</v>
+        <v>0.90878713933809718</v>
       </c>
       <c r="N47">
-        <v>-2.728014285872734E-2</v>
+        <v>-0.48110792741165259</v>
       </c>
       <c r="O47">
-        <v>3.8907728109478387E-2</v>
+        <v>2.92983987629159E-2</v>
       </c>
       <c r="P47" t="s">
         <v>22</v>
       </c>
       <c r="Q47">
-        <v>0.37200991839819358</v>
+        <v>0.30191759373752708</v>
       </c>
       <c r="R47">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="S47">
-        <v>118608625</v>
+        <v>133073425</v>
       </c>
       <c r="T47" t="s">
-        <v>75</v>
+        <v>28</v>
       </c>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="B48" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C48">
         <v>40</v>
       </c>
       <c r="D48">
+        <v>40</v>
+      </c>
+      <c r="E48">
+        <v>20</v>
+      </c>
+      <c r="F48">
+        <v>20</v>
+      </c>
+      <c r="G48">
+        <v>28</v>
+      </c>
+      <c r="H48">
         <v>12</v>
-      </c>
-      <c r="E48">
-        <v>6</v>
-      </c>
-      <c r="F48">
-        <v>6</v>
-      </c>
-      <c r="G48">
-        <v>10</v>
-      </c>
-      <c r="H48">
-        <v>2</v>
       </c>
       <c r="I48">
         <v>0</v>
       </c>
       <c r="J48">
-        <v>-1.012698031565394</v>
+        <v>-3.5089840038293629</v>
       </c>
       <c r="K48">
-        <v>3.4427380565077992E-2</v>
+        <v>3.047908883324827E-2</v>
       </c>
       <c r="L48">
-        <v>0.5974536339282428</v>
+        <v>5.7208266950534927</v>
       </c>
       <c r="M48">
-        <v>0.10847722996247421</v>
+        <v>3.8463423797685683E-4</v>
       </c>
       <c r="N48">
-        <v>-2.4282270186840068E-3</v>
+        <v>0.1034238044547323</v>
       </c>
       <c r="O48">
-        <v>0.82527684306091442</v>
+        <v>8.3714952198245152E-2</v>
       </c>
       <c r="P48" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="Q48">
-        <v>0.17213690282538999</v>
+        <v>0.33526997716573098</v>
       </c>
       <c r="R48">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="S48">
-        <v>118608625</v>
+        <v>42607288</v>
       </c>
       <c r="T48" t="s">
-        <v>75</v>
+        <v>37</v>
       </c>
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="B49" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="C49">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="D49">
+        <v>40</v>
+      </c>
+      <c r="E49">
+        <v>20</v>
+      </c>
+      <c r="F49">
+        <v>20</v>
+      </c>
+      <c r="G49">
+        <v>28</v>
+      </c>
+      <c r="H49">
         <v>12</v>
-      </c>
-      <c r="E49">
-        <v>6</v>
-      </c>
-      <c r="F49">
-        <v>6</v>
-      </c>
-      <c r="G49">
-        <v>10</v>
-      </c>
-      <c r="H49">
-        <v>2</v>
       </c>
       <c r="I49">
         <v>0</v>
       </c>
       <c r="J49">
-        <v>-1.012698031565394</v>
+        <v>-3.5089840038293629</v>
       </c>
       <c r="K49">
-        <v>3.4427380565077992E-2</v>
+        <v>3.047908883324827E-2</v>
       </c>
       <c r="L49">
-        <v>0.5974536339282428</v>
+        <v>5.7208266950534927</v>
       </c>
       <c r="M49">
-        <v>0.10847722996247421</v>
+        <v>3.8463423797685683E-4</v>
       </c>
       <c r="N49">
-        <v>-2.4282270186840068E-3</v>
+        <v>0.1034238044547323</v>
       </c>
       <c r="O49">
-        <v>0.82527684306091442</v>
+        <v>8.3714952198245152E-2</v>
       </c>
       <c r="P49" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="Q49">
-        <v>0.17213690282538999</v>
+        <v>0.33526997716573098</v>
       </c>
       <c r="R49">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="S49">
-        <v>118608625</v>
+        <v>42607288</v>
       </c>
       <c r="T49" t="s">
-        <v>75</v>
+        <v>37</v>
       </c>
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="B50" t="s">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="C50">
         <v>40</v>
@@ -3782,302 +3770,302 @@
         <v>20</v>
       </c>
       <c r="G50">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H50">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I50">
         <v>0</v>
       </c>
       <c r="J50">
-        <v>1.3249486110897579</v>
+        <v>0.34601732909138933</v>
       </c>
       <c r="K50">
-        <v>4.3355041183697478E-2</v>
+        <v>3.3357682946736078E-2</v>
       </c>
       <c r="L50">
-        <v>0.71266498876536533</v>
+        <v>0.1004527221784314</v>
       </c>
       <c r="M50">
-        <v>0.20839865114986519</v>
+        <v>0.34556460591557359</v>
       </c>
       <c r="N50">
-        <v>-4.0953058088131399E-2</v>
+        <v>-2.550493101614698E-3</v>
       </c>
       <c r="O50">
-        <v>6.4544023284892171E-2</v>
+        <v>0.55133194650996797</v>
       </c>
       <c r="P50" t="s">
         <v>22</v>
       </c>
       <c r="Q50">
-        <v>0.47690545302067228</v>
+        <v>0.36321521650315131</v>
       </c>
       <c r="R50">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="S50">
-        <v>118608625</v>
+        <v>121821143</v>
       </c>
       <c r="T50" t="s">
-        <v>75</v>
+        <v>34</v>
       </c>
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="B51" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C51">
         <v>40</v>
       </c>
       <c r="D51">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E51">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F51">
         <v>6</v>
       </c>
       <c r="G51">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H51">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J51">
-        <v>1.08973356350256</v>
+        <v>19.86724225142359</v>
       </c>
       <c r="K51">
-        <v>3.4202900276421061E-2</v>
+        <v>3.3448702010404931E-2</v>
       </c>
       <c r="L51">
-        <v>0.29996720448902198</v>
+        <v>0.24187050553734829</v>
       </c>
       <c r="M51">
-        <v>0.62591958482662369</v>
+        <v>0.9725811820548913</v>
       </c>
       <c r="N51">
-        <v>-3.5195709914695693E-2</v>
+        <v>-0.42986328445585731</v>
       </c>
       <c r="O51">
-        <v>0.14464277102510209</v>
+        <v>0.19693331425647789</v>
       </c>
       <c r="P51" t="s">
         <v>22</v>
       </c>
       <c r="Q51">
-        <v>0.17101450138210531</v>
+        <v>0.33448702010404929</v>
       </c>
       <c r="R51">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="S51">
-        <v>41637119</v>
+        <v>133073425</v>
       </c>
       <c r="T51" t="s">
-        <v>91</v>
+        <v>28</v>
       </c>
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="B52" t="s">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="C52">
         <v>40</v>
       </c>
       <c r="D52">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="E52">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F52">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="G52">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="H52">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I52">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J52">
-        <v>-0.89003657501142974</v>
+        <v>-1.001881651754355</v>
       </c>
       <c r="K52">
-        <v>4.9496135766188658E-2</v>
+        <v>3.3551779394062987E-2</v>
       </c>
       <c r="L52">
-        <v>-0.43471360459800129</v>
+        <v>-1.752337948302475</v>
       </c>
       <c r="M52">
-        <v>0.39313548293842532</v>
+        <v>1.8331903555406918E-2</v>
       </c>
       <c r="N52">
-        <v>2.5605120501600149E-2</v>
+        <v>-1.448179046297232E-2</v>
       </c>
       <c r="O52">
-        <v>0.19964765200577669</v>
+        <v>0.60004252353713872</v>
       </c>
       <c r="P52" t="s">
         <v>22</v>
       </c>
       <c r="Q52">
-        <v>0.2474806788309433</v>
+        <v>0.29487692425301382</v>
       </c>
       <c r="R52">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="S52">
-        <v>41637119</v>
+        <v>2128865</v>
       </c>
       <c r="T52" t="s">
-        <v>91</v>
+        <v>31</v>
       </c>
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>87</v>
+        <v>32</v>
       </c>
       <c r="B53" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C53">
         <v>40</v>
       </c>
       <c r="D53">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="E53">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="F53">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="G53">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="H53">
         <v>5</v>
       </c>
       <c r="I53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J53">
-        <v>1.08973356350256</v>
+        <v>2.469264590831818</v>
       </c>
       <c r="K53">
-        <v>3.4202900276421061E-2</v>
+        <v>3.3560134142751302E-2</v>
       </c>
       <c r="L53">
-        <v>0.29996720448902198</v>
+        <v>0.71776213690881407</v>
       </c>
       <c r="M53">
-        <v>0.62591958482662369</v>
+        <v>0.34554636315893827</v>
       </c>
       <c r="N53">
-        <v>-3.5195709914695693E-2</v>
+        <v>-1.8489579319539678E-2</v>
       </c>
       <c r="O53">
-        <v>0.14464277102510209</v>
+        <v>0.54556215281378595</v>
       </c>
       <c r="P53" t="s">
         <v>22</v>
       </c>
       <c r="Q53">
-        <v>0.17101450138210531</v>
+        <v>0.36502044827035662</v>
       </c>
       <c r="R53">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="S53">
-        <v>41613188</v>
+        <v>121821143</v>
       </c>
       <c r="T53" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>87</v>
+        <v>32</v>
       </c>
       <c r="B54" t="s">
-        <v>116</v>
+        <v>83</v>
       </c>
       <c r="C54">
         <v>40</v>
       </c>
       <c r="D54">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="E54">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="F54">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="G54">
+        <v>32</v>
+      </c>
+      <c r="H54">
         <v>5</v>
       </c>
-      <c r="H54">
-        <v>6</v>
-      </c>
       <c r="I54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J54">
-        <v>-0.89003657501142974</v>
+        <v>1.406060900941422</v>
       </c>
       <c r="K54">
-        <v>4.9496135766188658E-2</v>
+        <v>3.3560134432652752E-2</v>
       </c>
       <c r="L54">
-        <v>-0.43471360459800129</v>
+        <v>0.40871167953940057</v>
       </c>
       <c r="M54">
-        <v>0.39313548293842532</v>
+        <v>0.34554636339728789</v>
       </c>
       <c r="N54">
-        <v>2.5605120501600149E-2</v>
+        <v>-1.052842806067519E-2</v>
       </c>
       <c r="O54">
-        <v>0.19964765200577669</v>
+        <v>0.54556215272552311</v>
       </c>
       <c r="P54" t="s">
         <v>22</v>
       </c>
       <c r="Q54">
-        <v>0.2474806788309433</v>
+        <v>0.36502044812311579</v>
       </c>
       <c r="R54">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="S54">
-        <v>41613188</v>
+        <v>121821143</v>
       </c>
       <c r="T54" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="B55" t="s">
-        <v>36</v>
+        <v>84</v>
       </c>
       <c r="C55">
         <v>40</v>
@@ -4092,659 +4080,677 @@
         <v>20</v>
       </c>
       <c r="G55">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="H55">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I55">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J55">
-        <v>0.16446577887063091</v>
+        <v>-1.633196390048461</v>
       </c>
       <c r="K55">
-        <v>6.8882139630185926E-3</v>
+        <v>3.3720335007724478E-2</v>
       </c>
       <c r="L55">
-        <v>0.11159834567703091</v>
+        <v>-1.134036057819958</v>
       </c>
       <c r="M55">
-        <v>4.9357051286708427E-2</v>
+        <v>0.19721566055727069</v>
       </c>
       <c r="N55">
-        <v>-2.5423995537246251E-3</v>
+        <v>-4.8885893674578462E-2</v>
       </c>
       <c r="O55">
-        <v>0.23970748349274321</v>
+        <v>0.16093896671938479</v>
       </c>
       <c r="P55" t="s">
         <v>22</v>
       </c>
       <c r="Q55">
-        <v>7.5770353593204526E-2</v>
+        <v>0.37092368508496931</v>
       </c>
       <c r="R55">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S55">
-        <v>42607288</v>
+        <v>133073425</v>
       </c>
       <c r="T55" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="B56" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="C56">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="D56">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="E56">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="F56">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="G56">
+        <v>28</v>
+      </c>
+      <c r="H56">
         <v>9</v>
-      </c>
-      <c r="H56">
-        <v>5</v>
       </c>
       <c r="I56">
         <v>0</v>
       </c>
       <c r="J56">
-        <v>-6.4397121541658073</v>
+        <v>-0.82706409565323469</v>
       </c>
       <c r="K56">
-        <v>1.5464084997444279E-2</v>
+        <v>3.3819083490744882E-2</v>
       </c>
       <c r="L56">
-        <v>-2.8219310822468748</v>
+        <v>-0.75586117082043991</v>
       </c>
       <c r="M56">
-        <v>0.25055043391974419</v>
+        <v>2.8055946343789721E-2</v>
       </c>
       <c r="N56">
-        <v>-8.6833695823865936E-2</v>
+        <v>-2.728014285872734E-2</v>
       </c>
       <c r="O56">
-        <v>0.32965826370762719</v>
+        <v>3.8907728109478387E-2</v>
       </c>
       <c r="P56" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="Q56">
-        <v>0.11757799582230639</v>
+        <v>0.37200991839819358</v>
       </c>
       <c r="R56">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="S56">
-        <v>42607288</v>
+        <v>118608625</v>
       </c>
       <c r="T56" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B57" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C57">
         <v>40</v>
       </c>
       <c r="D57">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="E57">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="F57">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="G57">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="H57">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I57">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J57">
-        <v>-3.5089840038293629</v>
+        <v>-9.03164530592273</v>
       </c>
       <c r="K57">
-        <v>3.047908883324827E-2</v>
+        <v>3.4135658138946812E-2</v>
       </c>
       <c r="L57">
-        <v>5.7208266950534927</v>
+        <v>2.7150425066569022</v>
       </c>
       <c r="M57">
-        <v>3.8463423797685683E-4</v>
+        <v>0.66868773687714667</v>
       </c>
       <c r="N57">
-        <v>0.1034238044547323</v>
+        <v>0.86138538032827872</v>
       </c>
       <c r="O57">
-        <v>8.3714952198245152E-2</v>
+        <v>3.3789904319683679E-3</v>
       </c>
       <c r="P57" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="Q57">
-        <v>0.33526997716573098</v>
+        <v>0.34135658138946812</v>
       </c>
       <c r="R57">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="S57">
-        <v>42607288</v>
+        <v>2128865</v>
       </c>
       <c r="T57" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="B58" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="C58">
         <v>40</v>
       </c>
       <c r="D58">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="E58">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F58">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="G58">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="H58">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J58">
-        <v>-3.5089840038293629</v>
+        <v>1.08973356350256</v>
       </c>
       <c r="K58">
-        <v>3.047908883324827E-2</v>
+        <v>3.4202900276421061E-2</v>
       </c>
       <c r="L58">
-        <v>5.7208266950534927</v>
+        <v>0.29996720448902198</v>
       </c>
       <c r="M58">
-        <v>3.8463423797685683E-4</v>
+        <v>0.62591958482662369</v>
       </c>
       <c r="N58">
-        <v>0.1034238044547323</v>
+        <v>-3.5195709914695693E-2</v>
       </c>
       <c r="O58">
-        <v>8.3714952198245152E-2</v>
+        <v>0.14464277102510209</v>
       </c>
       <c r="P58" t="s">
         <v>22</v>
       </c>
       <c r="Q58">
-        <v>0.33526997716573098</v>
+        <v>0.17101450138210531</v>
       </c>
       <c r="R58">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="S58">
-        <v>42607288</v>
+        <v>41637119</v>
       </c>
       <c r="T58" t="s">
-        <v>37</v>
+        <v>91</v>
       </c>
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>35</v>
+        <v>87</v>
       </c>
       <c r="B59" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="C59">
         <v>40</v>
       </c>
       <c r="D59">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E59">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F59">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G59">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H59">
         <v>5</v>
       </c>
       <c r="I59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J59">
-        <v>-10.71718658034138</v>
+        <v>1.08973356350256</v>
       </c>
       <c r="K59">
-        <v>4.7351625403713279E-2</v>
+        <v>3.4202900276421061E-2</v>
+      </c>
+      <c r="L59">
+        <v>0.29996720448902198</v>
+      </c>
+      <c r="M59">
+        <v>0.62591958482662369</v>
       </c>
       <c r="N59">
-        <v>-4.6203649205414893E-2</v>
+        <v>-3.5195709914695693E-2</v>
       </c>
       <c r="O59">
-        <v>0.80516576253406069</v>
+        <v>0.14464277102510209</v>
       </c>
       <c r="P59" t="s">
         <v>22</v>
       </c>
       <c r="Q59">
-        <v>0.29042728810102098</v>
+        <v>0.17101450138210531</v>
       </c>
       <c r="R59">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="S59">
-        <v>42607288</v>
+        <v>41613188</v>
       </c>
       <c r="T59" t="s">
-        <v>37</v>
+        <v>89</v>
       </c>
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>29</v>
+        <v>74</v>
       </c>
       <c r="B60" t="s">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="C60">
         <v>40</v>
       </c>
       <c r="D60">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="E60">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F60">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="G60">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H60">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="I60">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J60">
-        <v>2.2661035835246768</v>
+        <v>-1.012698031565394</v>
       </c>
       <c r="K60">
-        <v>5.9187859599574601E-3</v>
+        <v>3.4427380565077992E-2</v>
       </c>
       <c r="L60">
-        <v>-2.0964034252115709</v>
+        <v>0.5974536339282428</v>
       </c>
       <c r="M60">
-        <v>9.0457591391094133E-2</v>
+        <v>0.10847722996247421</v>
       </c>
       <c r="N60">
-        <v>-3.2371214242875708E-2</v>
+        <v>-2.4282270186840068E-3</v>
       </c>
       <c r="O60">
-        <v>0.49214785518683102</v>
+        <v>0.82527684306091442</v>
       </c>
       <c r="P60" t="s">
         <v>22</v>
       </c>
       <c r="Q60">
-        <v>6.5106645559532064E-2</v>
+        <v>0.17213690282538999</v>
       </c>
       <c r="R60">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="S60">
-        <v>2128865</v>
+        <v>118608625</v>
       </c>
       <c r="T60" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>29</v>
+        <v>74</v>
       </c>
       <c r="B61" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="C61">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="D61">
         <v>12</v>
       </c>
       <c r="E61">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F61">
+        <v>6</v>
+      </c>
+      <c r="G61">
+        <v>10</v>
+      </c>
+      <c r="H61">
+        <v>2</v>
+      </c>
+      <c r="I61">
         <v>0</v>
       </c>
-      <c r="G61">
-        <v>6</v>
-      </c>
-      <c r="H61">
-        <v>3</v>
-      </c>
-      <c r="I61">
-        <v>3</v>
-      </c>
       <c r="J61">
-        <v>-22.803341363151539</v>
+        <v>-1.012698031565394</v>
       </c>
       <c r="K61">
-        <v>6.9086351900481419E-3</v>
+        <v>3.4427380565077992E-2</v>
+      </c>
+      <c r="L61">
+        <v>0.5974536339282428</v>
+      </c>
+      <c r="M61">
+        <v>0.10847722996247421</v>
       </c>
       <c r="N61">
-        <v>0.7579728903750047</v>
+        <v>-2.4282270186840068E-3</v>
       </c>
       <c r="O61">
-        <v>0.1292768105668764</v>
+        <v>0.82527684306091442</v>
       </c>
       <c r="P61" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="Q61">
-        <v>7.5994987090529556E-2</v>
+        <v>0.17213690282538999</v>
       </c>
       <c r="R61">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="S61">
-        <v>2128865</v>
+        <v>118608625</v>
       </c>
       <c r="T61" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>29</v>
+        <v>66</v>
       </c>
       <c r="B62" t="s">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="C62">
         <v>40</v>
       </c>
       <c r="D62">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="E62">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F62">
+        <v>20</v>
+      </c>
+      <c r="G62">
+        <v>35</v>
+      </c>
+      <c r="H62">
         <v>0</v>
       </c>
-      <c r="G62">
-        <v>6</v>
-      </c>
-      <c r="H62">
-        <v>3</v>
-      </c>
       <c r="I62">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J62">
-        <v>-22.803341363151539</v>
+        <v>13.02119382335745</v>
       </c>
       <c r="K62">
-        <v>6.9086351900481419E-3</v>
+        <v>3.4809696298399001E-2</v>
+      </c>
+      <c r="L62">
+        <v>-1.944933206533654</v>
+      </c>
+      <c r="M62">
+        <v>0.62300855776284758</v>
       </c>
       <c r="N62">
-        <v>0.7579728903750047</v>
+        <v>0.16133788277424541</v>
       </c>
       <c r="O62">
-        <v>0.1292768105668764</v>
+        <v>0.29200907890490818</v>
       </c>
       <c r="P62" t="s">
         <v>22</v>
       </c>
       <c r="Q62">
-        <v>7.5994987090529556E-2</v>
+        <v>0.38162727217358122</v>
       </c>
       <c r="R62">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="S62">
-        <v>2128865</v>
+        <v>11663173</v>
       </c>
       <c r="T62" t="s">
-        <v>31</v>
+        <v>68</v>
       </c>
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="B63" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C63">
         <v>40</v>
       </c>
       <c r="D63">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="E63">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F63">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="G63">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H63">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="I63">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J63">
-        <v>2.934218140550806E-2</v>
+        <v>3.3725483975789963E-2</v>
       </c>
       <c r="K63">
-        <v>1.233786693594505E-2</v>
+        <v>3.5040603635048143E-2</v>
       </c>
       <c r="L63">
-        <v>5.8009441696275928E-2</v>
+        <v>-1.152498033453846E-2</v>
       </c>
       <c r="M63">
-        <v>7.2567968168353956E-3</v>
+        <v>0.57765486833769542</v>
       </c>
       <c r="N63">
-        <v>-6.4529169307323768E-4</v>
+        <v>-6.0331087566292099E-4</v>
       </c>
       <c r="O63">
-        <v>0.2925022218747505</v>
+        <v>0.45559455732237808</v>
       </c>
       <c r="P63" t="s">
         <v>22</v>
       </c>
       <c r="Q63">
-        <v>0.12337866935945049</v>
+        <v>0.1886824812491586</v>
       </c>
       <c r="R63">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="S63">
-        <v>2128865</v>
+        <v>89522747</v>
       </c>
       <c r="T63" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="B64" t="s">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c r="C64">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="D64">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="E64">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="F64">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="G64">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H64">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="I64">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J64">
-        <v>2.934218140550806E-2</v>
+        <v>3.1070396841110771E-2</v>
       </c>
       <c r="K64">
-        <v>1.233786693594505E-2</v>
+        <v>3.5724564605321821E-2</v>
       </c>
       <c r="L64">
-        <v>5.8009441696275928E-2</v>
+        <v>1.472575294793871E-2</v>
       </c>
       <c r="M64">
-        <v>7.2567968168353956E-3</v>
+        <v>0.44700657425670159</v>
       </c>
       <c r="N64">
-        <v>-6.4529169307323768E-4</v>
+        <v>-6.9378304763142778E-4</v>
       </c>
       <c r="O64">
-        <v>0.2925022218747505</v>
+        <v>0.35735323418254311</v>
       </c>
       <c r="P64" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="Q64">
-        <v>0.12337866935945049</v>
+        <v>0.39297021065853999</v>
       </c>
       <c r="R64">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="S64">
-        <v>2128865</v>
+        <v>89522747</v>
       </c>
       <c r="T64" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B65" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="C65">
         <v>40</v>
       </c>
       <c r="D65">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E65">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F65">
         <v>6</v>
       </c>
       <c r="G65">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H65">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I65">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J65">
-        <v>7.5363006307403229E-3</v>
+        <v>19.9230123263353</v>
       </c>
       <c r="K65">
-        <v>2.495465211544555E-2</v>
+        <v>3.6247603352829387E-2</v>
       </c>
       <c r="L65">
-        <v>7.1933968130938851E-3</v>
+        <v>1.895096137558284</v>
       </c>
       <c r="M65">
-        <v>0.17782997038347961</v>
+        <v>0.79271640286172551</v>
       </c>
       <c r="N65">
-        <v>-9.4674345676398091E-5</v>
+        <v>-0.45388621491595948</v>
       </c>
       <c r="O65">
-        <v>0.59658396360251675</v>
+        <v>0.18413000494443749</v>
       </c>
       <c r="P65" t="s">
         <v>22</v>
       </c>
       <c r="Q65">
-        <v>0.13376644562604151</v>
+        <v>0.36247603352829388</v>
       </c>
       <c r="R65">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="S65">
-        <v>2128865</v>
+        <v>133073425</v>
       </c>
       <c r="T65" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B66" t="s">
-        <v>21</v>
+        <v>95</v>
       </c>
       <c r="C66">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="D66">
         <v>12</v>
@@ -4756,57 +4762,57 @@
         <v>6</v>
       </c>
       <c r="G66">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H66">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>-3.075692750799413</v>
+      </c>
+      <c r="K66">
+        <v>3.8472142615207372E-2</v>
+      </c>
+      <c r="L66">
+        <v>2.321863861175967</v>
+      </c>
+      <c r="M66">
+        <v>8.7676072707948749E-2</v>
+      </c>
+      <c r="N66">
+        <v>-1.654858862149642E-2</v>
+      </c>
+      <c r="O66">
+        <v>0.70649939137503515</v>
+      </c>
+      <c r="P66" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q66">
+        <v>0.38472142615207372</v>
+      </c>
+      <c r="R66">
         <v>3</v>
       </c>
-      <c r="J66">
-        <v>7.5363006307403229E-3</v>
-      </c>
-      <c r="K66">
-        <v>2.495465211544555E-2</v>
-      </c>
-      <c r="L66">
-        <v>7.1933968130938851E-3</v>
-      </c>
-      <c r="M66">
-        <v>0.17782997038347961</v>
-      </c>
-      <c r="N66">
-        <v>-9.4674345676398091E-5</v>
-      </c>
-      <c r="O66">
-        <v>0.59658396360251675</v>
-      </c>
-      <c r="P66" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q66">
-        <v>0.13376644562604151</v>
-      </c>
-      <c r="R66">
-        <v>17</v>
-      </c>
       <c r="S66">
-        <v>2128865</v>
+        <v>121821143</v>
       </c>
       <c r="T66" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B67" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="C67">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="D67">
         <v>12</v>
@@ -4818,108 +4824,108 @@
         <v>6</v>
       </c>
       <c r="G67">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H67">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>-3.075692750799413</v>
+      </c>
+      <c r="K67">
+        <v>3.8472142615207372E-2</v>
+      </c>
+      <c r="L67">
+        <v>2.321863861175967</v>
+      </c>
+      <c r="M67">
+        <v>8.7676072707948749E-2</v>
+      </c>
+      <c r="N67">
+        <v>-1.654858862149642E-2</v>
+      </c>
+      <c r="O67">
+        <v>0.70649939137503515</v>
+      </c>
+      <c r="P67" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q67">
+        <v>0.38472142615207372</v>
+      </c>
+      <c r="R67">
         <v>3</v>
       </c>
-      <c r="J67">
-        <v>0.45692675160538382</v>
-      </c>
-      <c r="K67">
-        <v>2.9622600616636231E-2</v>
-      </c>
-      <c r="L67">
-        <v>0.48246825304111418</v>
-      </c>
-      <c r="M67">
-        <v>0.15538786435449359</v>
-      </c>
-      <c r="N67">
-        <v>-7.903944870596322E-3</v>
-      </c>
-      <c r="O67">
-        <v>0.48714814763011799</v>
-      </c>
-      <c r="P67" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q67">
-        <v>0.17213690282538999</v>
-      </c>
-      <c r="R67">
-        <v>17</v>
-      </c>
       <c r="S67">
-        <v>2128865</v>
+        <v>121821143</v>
       </c>
       <c r="T67" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B68" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C68">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="D68">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="E68">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="F68">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="G68">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="H68">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="I68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J68">
-        <v>0.45692675160538382</v>
+        <v>-1.260038083591308E-2</v>
       </c>
       <c r="K68">
-        <v>2.9622600616636231E-2</v>
+        <v>3.8529988286322092E-2</v>
       </c>
       <c r="L68">
-        <v>0.48246825304111418</v>
+        <v>-9.3742665620836802E-4</v>
       </c>
       <c r="M68">
-        <v>0.15538786435449359</v>
+        <v>0.89173503949775013</v>
       </c>
       <c r="N68">
-        <v>-7.903944870596322E-3</v>
+        <v>-4.5548806548771951E-4</v>
       </c>
       <c r="O68">
-        <v>0.48714814763011799</v>
+        <v>0.10147547488379829</v>
       </c>
       <c r="P68" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="Q68">
-        <v>0.17213690282538999</v>
+        <v>0.14191087827643159</v>
       </c>
       <c r="R68">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="S68">
-        <v>2128865</v>
+        <v>133073425</v>
       </c>
       <c r="T68" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.2">
@@ -4927,16 +4933,16 @@
         <v>29</v>
       </c>
       <c r="B69" t="s">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="C69">
         <v>40</v>
       </c>
       <c r="D69">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E69">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F69">
         <v>20</v>
@@ -4945,34 +4951,34 @@
         <v>14</v>
       </c>
       <c r="H69">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I69">
         <v>8</v>
       </c>
       <c r="J69">
-        <v>-1.001881651754355</v>
+        <v>9.1328692982592004E-3</v>
       </c>
       <c r="K69">
-        <v>3.3551779394062987E-2</v>
+        <v>3.8702966802663157E-2</v>
       </c>
       <c r="L69">
-        <v>-1.752337948302475</v>
+        <v>-3.8500961585967971E-3</v>
       </c>
       <c r="M69">
-        <v>1.8331903555406918E-2</v>
+        <v>0.56138191023745354</v>
       </c>
       <c r="N69">
-        <v>-1.448179046297232E-2</v>
+        <v>-2.8977789364829389E-4</v>
       </c>
       <c r="O69">
-        <v>0.60004252353713872</v>
+        <v>0.26138129936831589</v>
       </c>
       <c r="P69" t="s">
         <v>22</v>
       </c>
       <c r="Q69">
-        <v>0.29487692425301382</v>
+        <v>0.14191087827643159</v>
       </c>
       <c r="R69">
         <v>17</v>
@@ -4986,188 +4992,188 @@
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B70" t="s">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="C70">
         <v>40</v>
       </c>
       <c r="D70">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E70">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F70">
         <v>6</v>
       </c>
       <c r="G70">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H70">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>-4.7508089873791903E-2</v>
+      </c>
+      <c r="K70">
+        <v>3.8705386228155392E-2</v>
+      </c>
+      <c r="L70">
+        <v>2.7597956615282089E-2</v>
+      </c>
+      <c r="M70">
+        <v>0.17345319209579019</v>
+      </c>
+      <c r="N70">
+        <v>3.4531165499371042E-4</v>
+      </c>
+      <c r="O70">
+        <v>0.61286362603629407</v>
+      </c>
+      <c r="P70" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q70">
+        <v>0.19352693114077699</v>
+      </c>
+      <c r="R70">
         <v>3</v>
       </c>
-      <c r="J70">
-        <v>-9.03164530592273</v>
-      </c>
-      <c r="K70">
-        <v>3.4135658138946812E-2</v>
-      </c>
-      <c r="L70">
-        <v>2.7150425066569022</v>
-      </c>
-      <c r="M70">
-        <v>0.66868773687714667</v>
-      </c>
-      <c r="N70">
-        <v>0.86138538032827872</v>
-      </c>
-      <c r="O70">
-        <v>3.3789904319683679E-3</v>
-      </c>
-      <c r="P70" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q70">
-        <v>0.34135658138946812</v>
-      </c>
-      <c r="R70">
-        <v>17</v>
-      </c>
       <c r="S70">
-        <v>2128865</v>
+        <v>121821143</v>
       </c>
       <c r="T70" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="71" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B71" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C71">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="D71">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="E71">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="F71">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="G71">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H71">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="I71">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J71">
-        <v>9.1328692982592004E-3</v>
+        <v>-4.7508089873791903E-2</v>
       </c>
       <c r="K71">
-        <v>3.8702966802663157E-2</v>
+        <v>3.8705386228155392E-2</v>
       </c>
       <c r="L71">
-        <v>-3.8500961585967971E-3</v>
+        <v>2.7597956615282089E-2</v>
       </c>
       <c r="M71">
-        <v>0.56138191023745354</v>
+        <v>0.17345319209579019</v>
       </c>
       <c r="N71">
-        <v>-2.8977789364829389E-4</v>
+        <v>3.4531165499371042E-4</v>
       </c>
       <c r="O71">
-        <v>0.26138129936831589</v>
+        <v>0.61286362603629407</v>
       </c>
       <c r="P71" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="Q71">
-        <v>0.14191087827643159</v>
+        <v>0.19352693114077699</v>
       </c>
       <c r="R71">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="S71">
-        <v>2128865</v>
+        <v>121821143</v>
       </c>
       <c r="T71" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="B72" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="C72">
         <v>40</v>
       </c>
       <c r="D72">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="E72">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F72">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="G72">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="H72">
+        <v>3</v>
+      </c>
+      <c r="I72">
         <v>0</v>
       </c>
-      <c r="I72">
-        <v>1</v>
-      </c>
       <c r="J72">
-        <v>12.7733473445151</v>
+        <v>-0.1358361978014499</v>
       </c>
       <c r="K72">
-        <v>2.336455351576475E-2</v>
+        <v>3.9734870410335257E-2</v>
       </c>
       <c r="L72">
-        <v>-1.018318786815763</v>
+        <v>-7.3151141816696616E-2</v>
       </c>
       <c r="M72">
-        <v>0.77655184377872344</v>
+        <v>0.18174505356414669</v>
       </c>
       <c r="N72">
-        <v>0.27412292260469179</v>
+        <v>-3.021475002552499E-3</v>
       </c>
       <c r="O72">
-        <v>5.3514792056003201E-2</v>
+        <v>0.13074478755273339</v>
       </c>
       <c r="P72" t="s">
         <v>22</v>
       </c>
       <c r="Q72">
-        <v>0.2570100886734123</v>
+        <v>0.39734870410335271</v>
       </c>
       <c r="R72">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="S72">
-        <v>11663173</v>
+        <v>121821143</v>
       </c>
       <c r="T72" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
     </row>
     <row r="73" spans="1:20" x14ac:dyDescent="0.2">
@@ -5175,22 +5181,22 @@
         <v>66</v>
       </c>
       <c r="B73" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="C73">
         <v>40</v>
       </c>
       <c r="D73">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E73">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F73">
         <v>20</v>
       </c>
       <c r="G73">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H73">
         <v>0</v>
@@ -5199,28 +5205,28 @@
         <v>1</v>
       </c>
       <c r="J73">
-        <v>12.30296935759703</v>
+        <v>13.334941814875201</v>
       </c>
       <c r="K73">
-        <v>2.5511422862639271E-2</v>
+        <v>3.9914323374207743E-2</v>
       </c>
       <c r="L73">
-        <v>-0.77550339143463309</v>
+        <v>-2.6534814437126539</v>
       </c>
       <c r="M73">
-        <v>0.82522015331433807</v>
+        <v>0.50482669965970328</v>
       </c>
       <c r="N73">
-        <v>0.29611640722063881</v>
+        <v>0.25356915396877411</v>
       </c>
       <c r="O73">
-        <v>3.4221852178898157E-2</v>
+        <v>0.1150785646266943</v>
       </c>
       <c r="P73" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="Q73">
-        <v>0.28062565148903201</v>
+        <v>0.43905755711628508</v>
       </c>
       <c r="R73">
         <v>8</v>
@@ -5234,72 +5240,72 @@
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="B74" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="C74">
         <v>40</v>
       </c>
       <c r="D74">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="E74">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F74">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="G74">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="H74">
+        <v>3</v>
+      </c>
+      <c r="I74">
         <v>0</v>
       </c>
-      <c r="I74">
-        <v>1</v>
-      </c>
       <c r="J74">
-        <v>13.02119382335745</v>
+        <v>5.404034172766789E-3</v>
       </c>
       <c r="K74">
-        <v>3.4809696298399001E-2</v>
+        <v>3.9928339884627212E-2</v>
       </c>
       <c r="L74">
-        <v>-1.944933206533654</v>
+        <v>2.342895536144988E-3</v>
       </c>
       <c r="M74">
-        <v>0.62300855776284758</v>
+        <v>0.30078310363563582</v>
       </c>
       <c r="N74">
-        <v>0.16133788277424541</v>
+        <v>-1.153086629104303E-4</v>
       </c>
       <c r="O74">
-        <v>0.29200907890490818</v>
+        <v>0.16383123103803501</v>
       </c>
       <c r="P74" t="s">
         <v>22</v>
       </c>
       <c r="Q74">
-        <v>0.38162727217358122</v>
+        <v>0.39928339884627212</v>
       </c>
       <c r="R74">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="S74">
-        <v>11663173</v>
+        <v>121821143</v>
       </c>
       <c r="T74" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
     </row>
     <row r="75" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="B75" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C75">
         <v>40</v>
@@ -5314,234 +5320,240 @@
         <v>20</v>
       </c>
       <c r="G75">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="H75">
+        <v>22</v>
+      </c>
+      <c r="I75">
+        <v>8</v>
+      </c>
+      <c r="J75">
+        <v>2.3600169437746192E-15</v>
+      </c>
+      <c r="K75">
+        <v>4.0259336436489872E-2</v>
+      </c>
+      <c r="L75">
+        <v>-2.0148961864054271E-15</v>
+      </c>
+      <c r="M75">
+        <v>0.17241969897700229</v>
+      </c>
+      <c r="N75">
+        <v>1</v>
+      </c>
+      <c r="O75">
         <v>0</v>
       </c>
-      <c r="I75">
-        <v>1</v>
-      </c>
-      <c r="J75">
-        <v>13.334941814875201</v>
-      </c>
-      <c r="K75">
-        <v>3.9914323374207743E-2</v>
-      </c>
-      <c r="L75">
-        <v>-2.6534814437126539</v>
-      </c>
-      <c r="M75">
-        <v>0.50482669965970328</v>
-      </c>
-      <c r="N75">
-        <v>0.25356915396877411</v>
-      </c>
-      <c r="O75">
-        <v>0.1150785646266943</v>
-      </c>
       <c r="P75" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="Q75">
-        <v>0.43905755711628508</v>
+        <v>0.36667720331576908</v>
       </c>
       <c r="R75">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="S75">
-        <v>11663173</v>
+        <v>13284922</v>
       </c>
       <c r="T75" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="B76" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C76">
         <v>40</v>
       </c>
       <c r="D76">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E76">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F76">
         <v>20</v>
       </c>
       <c r="G76">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="H76">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I76">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J76">
-        <v>13.26489049563196</v>
+        <v>-0.20260574613204471</v>
       </c>
       <c r="K76">
-        <v>4.0486938190639379E-2</v>
+        <v>4.0443435827340349E-2</v>
       </c>
       <c r="L76">
-        <v>-2.710118984070419</v>
+        <v>0.20020978373367571</v>
       </c>
       <c r="M76">
-        <v>0.49488193445594508</v>
+        <v>0.12755201420324741</v>
       </c>
       <c r="N76">
-        <v>0.25600534544771802</v>
+        <v>-6.3686101042650467E-4</v>
       </c>
       <c r="O76">
-        <v>0.1109796938273359</v>
+        <v>0.89891539428242662</v>
       </c>
       <c r="P76" t="s">
         <v>22</v>
       </c>
       <c r="Q76">
-        <v>0.44535632009703319</v>
+        <v>0.37470157170695279</v>
       </c>
       <c r="R76">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="S76">
-        <v>11663173</v>
+        <v>89522747</v>
       </c>
       <c r="T76" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B77" t="s">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="C77">
         <v>40</v>
       </c>
       <c r="D77">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E77">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F77">
         <v>20</v>
       </c>
       <c r="G77">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="H77">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I77">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J77">
-        <v>2.702782975910396E-2</v>
+        <v>13.26489049563196</v>
       </c>
       <c r="K77">
-        <v>2.5083651135668919E-2</v>
+        <v>4.0486938190639379E-2</v>
       </c>
       <c r="L77">
-        <v>2.255206296369511E-3</v>
+        <v>-2.710118984070419</v>
       </c>
       <c r="M77">
-        <v>0.88704585858769081</v>
+        <v>0.49488193445594508</v>
       </c>
       <c r="N77">
-        <v>-8.0503850748489536E-4</v>
+        <v>0.25600534544771802</v>
       </c>
       <c r="O77">
-        <v>0.19213886307957151</v>
+        <v>0.1109796938273359</v>
       </c>
       <c r="P77" t="s">
         <v>22</v>
       </c>
       <c r="Q77">
-        <v>0.19317208872234379</v>
+        <v>0.44535632009703319</v>
       </c>
       <c r="R77">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="S77">
-        <v>46921566</v>
+        <v>11663173</v>
       </c>
       <c r="T77" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="B78" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C78">
         <v>40</v>
       </c>
       <c r="D78">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="E78">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F78">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G78">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H78">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="I78">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J78">
-        <v>1.2777587974034881</v>
+        <v>-1.4459036074786811</v>
       </c>
       <c r="K78">
-        <v>4.1721825150055292E-2</v>
+        <v>4.0542723384057462E-2</v>
+      </c>
+      <c r="L78">
+        <v>1.4400158682288371</v>
+      </c>
+      <c r="M78">
+        <v>0.1248867679914118</v>
       </c>
       <c r="N78">
-        <v>2.2292449607106281E-2</v>
+        <v>-4.5906516239240438E-3</v>
       </c>
       <c r="O78">
-        <v>0.22750292690258561</v>
+        <v>0.89795903610099603</v>
       </c>
       <c r="P78" t="s">
         <v>22</v>
       </c>
       <c r="Q78">
-        <v>0.33377460120044228</v>
+        <v>0.38425609714036352</v>
       </c>
       <c r="R78">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="S78">
-        <v>46921566</v>
+        <v>89522747</v>
       </c>
       <c r="T78" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="B79" t="s">
-        <v>33</v>
+        <v>104</v>
       </c>
       <c r="C79">
         <v>40</v>
@@ -5556,46 +5568,46 @@
         <v>20</v>
       </c>
       <c r="G79">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H79">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="I79">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J79">
-        <v>0.19616165625288989</v>
+        <v>-0.82333361080917555</v>
       </c>
       <c r="K79">
-        <v>6.8073684116259619E-3</v>
+        <v>4.0542723438265302E-2</v>
       </c>
       <c r="L79">
-        <v>5.8552663515730997E-2</v>
+        <v>0.81998098654543516</v>
       </c>
       <c r="M79">
-        <v>0.20972011051297329</v>
+        <v>0.124886767452096</v>
       </c>
       <c r="N79">
-        <v>-3.3662396458685379E-3</v>
+        <v>-2.614031648958624E-3</v>
       </c>
       <c r="O79">
-        <v>7.7512667228128274E-2</v>
+        <v>0.89795903575976854</v>
       </c>
       <c r="P79" t="s">
         <v>22</v>
       </c>
       <c r="Q79">
-        <v>7.4881052527885586E-2</v>
+        <v>0.38425609630441437</v>
       </c>
       <c r="R79">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="S79">
-        <v>121821143</v>
+        <v>89522747</v>
       </c>
       <c r="T79" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
     </row>
     <row r="80" spans="1:20" x14ac:dyDescent="0.2">
@@ -5603,52 +5615,52 @@
         <v>32</v>
       </c>
       <c r="B80" t="s">
-        <v>47</v>
+        <v>105</v>
       </c>
       <c r="C80">
         <v>40</v>
       </c>
       <c r="D80">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="E80">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="F80">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="G80">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="H80">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I80">
         <v>0</v>
       </c>
       <c r="J80">
-        <v>-4.0130514757324862</v>
+        <v>-2.5873615783787338</v>
       </c>
       <c r="K80">
-        <v>1.047870001632694E-2</v>
+        <v>4.0999453973508203E-2</v>
       </c>
       <c r="L80">
-        <v>-2.457130685960335</v>
+        <v>1.884669511622717</v>
       </c>
       <c r="M80">
-        <v>1.8990177697616881E-2</v>
+        <v>0.1021446098599801</v>
       </c>
       <c r="N80">
-        <v>6.1737799047181748E-2</v>
+        <v>-1.281855474175375E-2</v>
       </c>
       <c r="O80">
-        <v>0.13416257351562119</v>
+        <v>0.73287501390304843</v>
       </c>
       <c r="P80" t="s">
         <v>22</v>
       </c>
       <c r="Q80">
-        <v>0.11526570017959641</v>
+        <v>0.40999453973508199</v>
       </c>
       <c r="R80">
         <v>3</v>
@@ -5662,134 +5674,128 @@
     </row>
     <row r="81" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="B81" t="s">
-        <v>64</v>
+        <v>106</v>
       </c>
       <c r="C81">
         <v>40</v>
       </c>
       <c r="D81">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E81">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F81">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G81">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H81">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I81">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J81">
-        <v>-12.263010912480521</v>
+        <v>1.2777587974034881</v>
       </c>
       <c r="K81">
-        <v>1.878230462299495E-2</v>
-      </c>
-      <c r="L81">
-        <v>2.9137970146023302</v>
-      </c>
-      <c r="M81">
-        <v>0.46661628770213909</v>
+        <v>4.1721825150055292E-2</v>
       </c>
       <c r="N81">
-        <v>-0.2199971736394063</v>
+        <v>2.2292449607106281E-2</v>
       </c>
       <c r="O81">
-        <v>0.14488849165586709</v>
+        <v>0.22750292690258561</v>
       </c>
       <c r="P81" t="s">
         <v>22</v>
       </c>
       <c r="Q81">
-        <v>0.1878230462299495</v>
+        <v>0.33377460120044228</v>
       </c>
       <c r="R81">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="S81">
-        <v>121821143</v>
+        <v>46921566</v>
       </c>
       <c r="T81" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
     </row>
     <row r="82" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B82" t="s">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="C82">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="D82">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="E82">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="F82">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="G82">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="H82">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I82">
         <v>0</v>
       </c>
       <c r="J82">
-        <v>0.34601732909138933</v>
+        <v>-11.21660759836565</v>
       </c>
       <c r="K82">
-        <v>3.3357682946736078E-2</v>
+        <v>4.2135399271503018E-2</v>
       </c>
       <c r="L82">
-        <v>0.1004527221784314</v>
+        <v>8.0113320842457032</v>
       </c>
       <c r="M82">
-        <v>0.34556460591557359</v>
+        <v>8.2073645054145314E-2</v>
       </c>
       <c r="N82">
-        <v>-2.550493101614698E-3</v>
+        <v>-5.579132711799388E-2</v>
       </c>
       <c r="O82">
-        <v>0.55133194650996797</v>
+        <v>0.77830569067477429</v>
       </c>
       <c r="P82" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="Q82">
-        <v>0.36321521650315131</v>
+        <v>0.42135399271503021</v>
       </c>
       <c r="R82">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S82">
-        <v>121821143</v>
+        <v>133073425</v>
       </c>
       <c r="T82" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="83" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="B83" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="C83">
         <v>40</v>
@@ -5804,54 +5810,54 @@
         <v>20</v>
       </c>
       <c r="G83">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="H83">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="I83">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J83">
-        <v>2.469264590831818</v>
+        <v>2.4132537111800582E-2</v>
       </c>
       <c r="K83">
-        <v>3.3560134142751302E-2</v>
+        <v>4.2642894750632231E-2</v>
       </c>
       <c r="L83">
-        <v>0.71776213690881407</v>
+        <v>-7.375577523820686E-3</v>
       </c>
       <c r="M83">
-        <v>0.34554636315893827</v>
+        <v>0.63057486905350801</v>
       </c>
       <c r="N83">
-        <v>-1.8489579319539678E-2</v>
+        <v>-3.4607493422119111E-5</v>
       </c>
       <c r="O83">
-        <v>0.54556215281378595</v>
+        <v>0.95528232059194007</v>
       </c>
       <c r="P83" t="s">
         <v>22</v>
       </c>
       <c r="Q83">
-        <v>0.36502044827035662</v>
+        <v>0.19317208872234379</v>
       </c>
       <c r="R83">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S83">
-        <v>121821143</v>
+        <v>13284922</v>
       </c>
       <c r="T83" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
     </row>
     <row r="84" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="B84" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="C84">
         <v>40</v>
@@ -5866,108 +5872,108 @@
         <v>20</v>
       </c>
       <c r="G84">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H84">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I84">
         <v>0</v>
       </c>
       <c r="J84">
-        <v>1.406060900941422</v>
+        <v>1.3249486110897579</v>
       </c>
       <c r="K84">
-        <v>3.3560134432652752E-2</v>
+        <v>4.3355041183697478E-2</v>
       </c>
       <c r="L84">
-        <v>0.40871167953940057</v>
+        <v>0.71266498876536533</v>
       </c>
       <c r="M84">
-        <v>0.34554636339728789</v>
+        <v>0.20839865114986519</v>
       </c>
       <c r="N84">
-        <v>-1.052842806067519E-2</v>
+        <v>-4.0953058088131399E-2</v>
       </c>
       <c r="O84">
-        <v>0.54556215272552311</v>
+        <v>6.4544023284892171E-2</v>
       </c>
       <c r="P84" t="s">
         <v>22</v>
       </c>
       <c r="Q84">
-        <v>0.36502044812311579</v>
+        <v>0.47690545302067228</v>
       </c>
       <c r="R84">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="S84">
-        <v>121821143</v>
+        <v>118608625</v>
       </c>
       <c r="T84" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
     </row>
     <row r="85" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B85" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="C85">
         <v>40</v>
       </c>
       <c r="D85">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="E85">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="F85">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="G85">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="H85">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="I85">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J85">
-        <v>-3.075692750799413</v>
+        <v>-0.64182551778097552</v>
       </c>
       <c r="K85">
-        <v>3.8472142615207372E-2</v>
+        <v>4.4623548675940997E-2</v>
       </c>
       <c r="L85">
-        <v>2.321863861175967</v>
+        <v>-0.67899955839014736</v>
       </c>
       <c r="M85">
-        <v>8.7676072707948749E-2</v>
+        <v>6.7666380951470359E-2</v>
       </c>
       <c r="N85">
-        <v>-1.654858862149642E-2</v>
+        <v>-2.978751349915873E-2</v>
       </c>
       <c r="O85">
-        <v>0.70649939137503515</v>
+        <v>4.3910887462403618E-2</v>
       </c>
       <c r="P85" t="s">
         <v>22</v>
       </c>
       <c r="Q85">
-        <v>0.38472142615207372</v>
+        <v>0.28107287101966988</v>
       </c>
       <c r="R85">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S85">
-        <v>121821143</v>
+        <v>133073425</v>
       </c>
       <c r="T85" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="86" spans="1:20" x14ac:dyDescent="0.2">
@@ -5975,10 +5981,10 @@
         <v>32</v>
       </c>
       <c r="B86" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="C86">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="D86">
         <v>12</v>
@@ -5999,28 +6005,28 @@
         <v>0</v>
       </c>
       <c r="J86">
-        <v>-3.075692750799413</v>
+        <v>7.9533659242073904</v>
       </c>
       <c r="K86">
-        <v>3.8472142615207372E-2</v>
+        <v>4.4773337734243947E-2</v>
       </c>
       <c r="L86">
-        <v>2.321863861175967</v>
+        <v>5.3915123119684853</v>
       </c>
       <c r="M86">
-        <v>8.7676072707948749E-2</v>
+        <v>0.1318925866531683</v>
       </c>
       <c r="N86">
-        <v>-1.654858862149642E-2</v>
+        <v>-0.19994425905978611</v>
       </c>
       <c r="O86">
-        <v>0.70649939137503515</v>
+        <v>0.1178768868021631</v>
       </c>
       <c r="P86" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="Q86">
-        <v>0.38472142615207372</v>
+        <v>0.44773337734243951</v>
       </c>
       <c r="R86">
         <v>3</v>
@@ -6034,250 +6040,244 @@
     </row>
     <row r="87" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="B87" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C87">
         <v>40</v>
       </c>
       <c r="D87">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="E87">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F87">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="G87">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H87">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="I87">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J87">
-        <v>-4.7508089873791903E-2</v>
+        <v>1.802877254547621</v>
       </c>
       <c r="K87">
-        <v>3.8705386228155392E-2</v>
+        <v>4.5166804094122083E-2</v>
       </c>
       <c r="L87">
-        <v>2.7597956615282089E-2</v>
+        <v>-4.4303820204361672</v>
       </c>
       <c r="M87">
-        <v>0.17345319209579019</v>
+        <v>3.7034618687144618E-4</v>
       </c>
       <c r="N87">
-        <v>3.4531165499371042E-4</v>
+        <v>2.693100153898613E-2</v>
       </c>
       <c r="O87">
-        <v>0.61286362603629407</v>
+        <v>0.55291929856072264</v>
       </c>
       <c r="P87" t="s">
         <v>22</v>
       </c>
       <c r="Q87">
-        <v>0.19352693114077699</v>
+        <v>0.49683484503534281</v>
       </c>
       <c r="R87">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="S87">
-        <v>121821143</v>
+        <v>89522747</v>
       </c>
       <c r="T87" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
     </row>
     <row r="88" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="B88" t="s">
-        <v>27</v>
+        <v>110</v>
       </c>
       <c r="C88">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="D88">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="E88">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F88">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="G88">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H88">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="I88">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J88">
-        <v>-4.7508089873791903E-2</v>
+        <v>6.1393131425740251</v>
       </c>
       <c r="K88">
-        <v>3.8705386228155392E-2</v>
+        <v>4.7232885865909388E-2</v>
       </c>
       <c r="L88">
-        <v>2.7597956615282089E-2</v>
+        <v>3.1811670589206789</v>
       </c>
       <c r="M88">
-        <v>0.17345319209579019</v>
+        <v>0.41998463166520378</v>
       </c>
       <c r="N88">
-        <v>3.4531165499371042E-4</v>
+        <v>0.57083849457037894</v>
       </c>
       <c r="O88">
-        <v>0.61286362603629407</v>
+        <v>1.1064646930455961E-3</v>
       </c>
       <c r="P88" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="Q88">
-        <v>0.19352693114077699</v>
+        <v>0.51956174452500326</v>
       </c>
       <c r="R88">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S88">
-        <v>121821143</v>
+        <v>13284922</v>
       </c>
       <c r="T88" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
     </row>
     <row r="89" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="B89" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="C89">
         <v>40</v>
       </c>
       <c r="D89">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="E89">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F89">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="G89">
         <v>10</v>
       </c>
       <c r="H89">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="I89">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J89">
-        <v>-0.1358361978014499</v>
+        <v>6.1393131425740251</v>
       </c>
       <c r="K89">
-        <v>3.9734870410335257E-2</v>
+        <v>4.7232885865909388E-2</v>
       </c>
       <c r="L89">
-        <v>-7.3151141816696616E-2</v>
+        <v>3.1811670589206789</v>
       </c>
       <c r="M89">
-        <v>0.18174505356414669</v>
+        <v>0.41998463166520378</v>
       </c>
       <c r="N89">
-        <v>-3.021475002552499E-3</v>
+        <v>0.57083849457037894</v>
       </c>
       <c r="O89">
-        <v>0.13074478755273339</v>
+        <v>1.1064646930455961E-3</v>
       </c>
       <c r="P89" t="s">
         <v>22</v>
       </c>
       <c r="Q89">
-        <v>0.39734870410335271</v>
+        <v>0.51956174452500326</v>
       </c>
       <c r="R89">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S89">
-        <v>121821143</v>
+        <v>13284922</v>
       </c>
       <c r="T89" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
     </row>
     <row r="90" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B90" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="C90">
         <v>40</v>
       </c>
       <c r="D90">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E90">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F90">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G90">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H90">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I90">
         <v>0</v>
       </c>
       <c r="J90">
-        <v>5.404034172766789E-3</v>
+        <v>-10.71718658034138</v>
       </c>
       <c r="K90">
-        <v>3.9928339884627212E-2</v>
-      </c>
-      <c r="L90">
-        <v>2.342895536144988E-3</v>
-      </c>
-      <c r="M90">
-        <v>0.30078310363563582</v>
+        <v>4.7351625403713279E-2</v>
       </c>
       <c r="N90">
-        <v>-1.153086629104303E-4</v>
+        <v>-4.6203649205414893E-2</v>
       </c>
       <c r="O90">
-        <v>0.16383123103803501</v>
+        <v>0.80516576253406069</v>
       </c>
       <c r="P90" t="s">
         <v>22</v>
       </c>
       <c r="Q90">
-        <v>0.39928339884627212</v>
+        <v>0.29042728810102098</v>
       </c>
       <c r="R90">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S90">
-        <v>121821143</v>
+        <v>42607288</v>
       </c>
       <c r="T90" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="91" spans="1:20" x14ac:dyDescent="0.2">
@@ -6285,7 +6285,7 @@
         <v>32</v>
       </c>
       <c r="B91" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="C91">
         <v>40</v>
@@ -6309,28 +6309,28 @@
         <v>0</v>
       </c>
       <c r="J91">
-        <v>-2.5873615783787338</v>
+        <v>0.34386803647827252</v>
       </c>
       <c r="K91">
-        <v>4.0999453973508203E-2</v>
+        <v>4.7985693571560517E-2</v>
       </c>
       <c r="L91">
-        <v>1.884669511622717</v>
+        <v>0.15686281360463861</v>
       </c>
       <c r="M91">
-        <v>0.1021446098599801</v>
+        <v>0.30006040318773469</v>
       </c>
       <c r="N91">
-        <v>-1.281855474175375E-2</v>
+        <v>-8.1873665733709008E-3</v>
       </c>
       <c r="O91">
-        <v>0.73287501390304843</v>
+        <v>0.1421096760922759</v>
       </c>
       <c r="P91" t="s">
         <v>22</v>
       </c>
       <c r="Q91">
-        <v>0.40999453973508199</v>
+        <v>0.47985693571560523</v>
       </c>
       <c r="R91">
         <v>3</v>
@@ -6347,10 +6347,10 @@
         <v>32</v>
       </c>
       <c r="B92" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C92">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="D92">
         <v>12</v>
@@ -6371,28 +6371,28 @@
         <v>0</v>
       </c>
       <c r="J92">
-        <v>7.9533659242073904</v>
+        <v>0.34386803647827252</v>
       </c>
       <c r="K92">
-        <v>4.4773337734243947E-2</v>
+        <v>4.7985693571560517E-2</v>
       </c>
       <c r="L92">
-        <v>5.3915123119684853</v>
+        <v>0.15686281360463861</v>
       </c>
       <c r="M92">
-        <v>0.1318925866531683</v>
+        <v>0.30006040318773469</v>
       </c>
       <c r="N92">
-        <v>-0.19994425905978611</v>
+        <v>-8.1873665733709008E-3</v>
       </c>
       <c r="O92">
-        <v>0.1178768868021631</v>
+        <v>0.1421096760922759</v>
       </c>
       <c r="P92" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="Q92">
-        <v>0.44773337734243951</v>
+        <v>0.47985693571560523</v>
       </c>
       <c r="R92">
         <v>3</v>
@@ -6409,10 +6409,10 @@
         <v>32</v>
       </c>
       <c r="B93" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C93">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="D93">
         <v>12</v>
@@ -6451,7 +6451,7 @@
         <v>0.1421096760922759</v>
       </c>
       <c r="P93" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="Q93">
         <v>0.47985693571560523</v>
@@ -6468,13 +6468,13 @@
     </row>
     <row r="94" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>32</v>
+        <v>90</v>
       </c>
       <c r="B94" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C94">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="D94">
         <v>12</v>
@@ -6486,57 +6486,57 @@
         <v>6</v>
       </c>
       <c r="G94">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H94">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J94">
-        <v>0.34386803647827252</v>
+        <v>-0.89003657501142974</v>
       </c>
       <c r="K94">
-        <v>4.7985693571560517E-2</v>
+        <v>4.9496135766188658E-2</v>
       </c>
       <c r="L94">
-        <v>0.15686281360463861</v>
+        <v>-0.43471360459800129</v>
       </c>
       <c r="M94">
-        <v>0.30006040318773469</v>
+        <v>0.39313548293842532</v>
       </c>
       <c r="N94">
-        <v>-8.1873665733709008E-3</v>
+        <v>2.5605120501600149E-2</v>
       </c>
       <c r="O94">
-        <v>0.1421096760922759</v>
+        <v>0.19964765200577669</v>
       </c>
       <c r="P94" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="Q94">
-        <v>0.47985693571560523</v>
+        <v>0.2474806788309433</v>
       </c>
       <c r="R94">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="S94">
-        <v>121821143</v>
+        <v>41637119</v>
       </c>
       <c r="T94" t="s">
-        <v>34</v>
+        <v>91</v>
       </c>
     </row>
     <row r="95" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>32</v>
+        <v>87</v>
       </c>
       <c r="B95" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C95">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="D95">
         <v>12</v>
@@ -6548,52 +6548,52 @@
         <v>6</v>
       </c>
       <c r="G95">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H95">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J95">
-        <v>0.34386803647827252</v>
+        <v>-0.89003657501142974</v>
       </c>
       <c r="K95">
-        <v>4.7985693571560517E-2</v>
+        <v>4.9496135766188658E-2</v>
       </c>
       <c r="L95">
-        <v>0.15686281360463861</v>
+        <v>-0.43471360459800129</v>
       </c>
       <c r="M95">
-        <v>0.30006040318773469</v>
+        <v>0.39313548293842532</v>
       </c>
       <c r="N95">
-        <v>-8.1873665733709008E-3</v>
+        <v>2.5605120501600149E-2</v>
       </c>
       <c r="O95">
-        <v>0.1421096760922759</v>
+        <v>0.19964765200577669</v>
       </c>
       <c r="P95" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="Q95">
-        <v>0.47985693571560523</v>
+        <v>0.2474806788309433</v>
       </c>
       <c r="R95">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="S95">
-        <v>121821143</v>
+        <v>41613188</v>
       </c>
       <c r="T95" t="s">
-        <v>34</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T95">
+    <sortCondition ref="K2:K95"/>
     <sortCondition descending="1" ref="T2:T95"/>
-    <sortCondition ref="K2:K95"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/andean_associations/Andean Associations.xlsx
+++ b/andean_associations/Andean Associations.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11214"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wgu/Desktop/CMSNetwork/andean_associations/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wanjun/Desktop/CMSNetwork/andean_associations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38473A16-FB1C-874B-9015-7CB3FB7ADE57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDDC66FE-56E6-7D4C-9191-651E1B22F30E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25680" yWindow="660" windowWidth="25360" windowHeight="20780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="18440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
